--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C765037A-B889-4961-9153-25783B0AF900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C8097E-DF50-43F8-99B1-FB574575626A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4875" uniqueCount="633">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3909,10 +3909,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-l-mon-whtap03</t>
   </si>
   <si>
@@ -3952,6 +3948,30 @@
   </si>
   <si>
     <t>PBProtocol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-l-if-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-if-icsweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.135.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/5 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4440,7 +4460,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4773,6 +4793,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5808,8 +5831,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF73" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
-  <autoFilter ref="B1:AF73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF74" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="B1:AF74" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
@@ -6845,10 +6868,10 @@
         <v>112</v>
       </c>
       <c r="M1" s="79" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="N1" s="72" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="O1" s="101" t="s">
         <v>122</v>
@@ -6902,7 +6925,7 @@
         <v>8080</v>
       </c>
       <c r="L2" s="74" t="str">
-        <f t="shared" ref="L2:L19" si="3">SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(N2="", "", N2)</f>
+        <f t="shared" ref="L2:L21" si="3">SUBSTITUTE(D2, "hazr-", "")&amp;"-pb"&amp;IF(N2="", "", N2)</f>
         <v>t-dtg-web-lb-pb8080</v>
       </c>
       <c r="M2" s="74" t="s">
@@ -7975,97 +7998,111 @@
       <c r="D20" s="86" t="s">
         <v>364</v>
       </c>
-      <c r="E20" s="86"/>
+      <c r="E20" s="74" t="str">
+        <f t="shared" ref="E20:E27" si="4">SUBSTITUTE(D20, "hazr-", "")&amp;"-rule"&amp;N20</f>
+        <v>t-dtg-cdstap-lb-rule9305</v>
+      </c>
       <c r="F20" s="86" t="str">
         <f t="shared" si="1"/>
         <v>t-dtg-cdstap-lb-fe</v>
       </c>
-      <c r="G20" s="86" t="s">
+      <c r="G20" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86" t="b">
+      <c r="H20" s="74">
+        <v>9305</v>
+      </c>
+      <c r="I20" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="86" t="str">
-        <f t="shared" si="2"/>
+      <c r="J20" s="74" t="str">
+        <f t="shared" ref="J20:J21" si="5">SUBSTITUTE(D20, "hazr-", "")&amp;"-bp"</f>
         <v>t-dtg-cdstap-lb-bp</v>
       </c>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86">
+      <c r="K20" s="74">
+        <v>9305</v>
+      </c>
+      <c r="L20" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdstap-lb-pb9305</v>
+      </c>
+      <c r="M20" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="74">
+        <v>9305</v>
+      </c>
+      <c r="O20" s="74">
         <v>4</v>
       </c>
-      <c r="P20" s="86" t="s">
+      <c r="P20" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="Q20" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" s="86" t="b">
+      <c r="Q20" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="84" t="s">
-        <v>184</v>
-      </c>
-      <c r="B21" s="84" t="str" cm="1">
+      <c r="A21" s="86" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="86" t="str" cm="1">
         <f t="array" ref="B21">UPPER(INDEX(_xlfn.TEXTSPLIT($C21, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="86" t="s">
         <v>389</v>
       </c>
-      <c r="D21" s="84" t="s">
-        <v>363</v>
-      </c>
-      <c r="E21" s="84" t="str">
-        <f t="shared" ref="E21:E27" si="4">SUBSTITUTE(D21, "hazr-", "")&amp;"-rule"&amp;N21</f>
-        <v>t-dtg-cdmlap-lb-rule9305</v>
-      </c>
-      <c r="F21" s="84" t="str">
-        <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap-lb-fe</v>
-      </c>
-      <c r="G21" s="84" t="s">
+      <c r="D21" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="E21" s="74" t="str">
+        <f t="shared" si="4"/>
+        <v>t-dtg-cdstap-lb-rule9306</v>
+      </c>
+      <c r="F21" s="86" t="str">
+        <f t="shared" ref="F21" si="6">SUBSTITUTE(D21, "hazr-", "")&amp;"-fe"</f>
+        <v>t-dtg-cdstap-lb-fe</v>
+      </c>
+      <c r="G21" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="I21" s="84" t="b">
+      <c r="H21" s="74">
+        <v>9306</v>
+      </c>
+      <c r="I21" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="84" t="str">
-        <f t="shared" si="2"/>
-        <v>t-dtg-cdmlap-lb-bp</v>
-      </c>
-      <c r="K21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="L21" s="84" t="str">
-        <f t="shared" ref="L21:L27" si="5">SUBSTITUTE(D21, "hazr-", "")&amp;"-pb"&amp;IF(N21="", "", N21)</f>
-        <v>t-dtg-cdmlap-lb-pb9305</v>
-      </c>
-      <c r="M21" s="84" t="s">
+      <c r="J21" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>t-dtg-cdstap-lb-bp</v>
+      </c>
+      <c r="K21" s="74">
+        <v>9306</v>
+      </c>
+      <c r="L21" s="74" t="str">
+        <f t="shared" si="3"/>
+        <v>t-dtg-cdstap-lb-pb9306</v>
+      </c>
+      <c r="M21" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="N21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="O21" s="84">
+      <c r="N21" s="74">
+        <v>9306</v>
+      </c>
+      <c r="O21" s="74">
         <v>4</v>
       </c>
-      <c r="P21" s="84" t="s">
+      <c r="P21" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="Q21" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" s="84" t="b">
+      <c r="Q21" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8083,10 +8120,7 @@
       <c r="D22" s="84" t="s">
         <v>363</v>
       </c>
-      <c r="E22" s="84" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dtg-cdmlap-lb-rule9306</v>
-      </c>
+      <c r="E22" s="84"/>
       <c r="F22" s="84" t="str">
         <f t="shared" si="1"/>
         <v>t-dtg-cdmlap-lb-fe</v>
@@ -8094,9 +8128,7 @@
       <c r="G22" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="84">
-        <v>9306</v>
-      </c>
+      <c r="H22" s="84"/>
       <c r="I22" s="84" t="b">
         <v>0</v>
       </c>
@@ -8104,19 +8136,10 @@
         <f t="shared" si="2"/>
         <v>t-dtg-cdmlap-lb-bp</v>
       </c>
-      <c r="K22" s="84">
-        <v>9306</v>
-      </c>
-      <c r="L22" s="84" t="str">
-        <f t="shared" si="5"/>
-        <v>t-dtg-cdmlap-lb-pb9306</v>
-      </c>
-      <c r="M22" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="84">
-        <v>9306</v>
-      </c>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
       <c r="O22" s="84">
         <v>4</v>
       </c>
@@ -8169,7 +8192,7 @@
         <v>8080</v>
       </c>
       <c r="L23" s="86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L23:L27" si="7">SUBSTITUTE(D23, "hazr-", "")&amp;"-pb"&amp;IF(N23="", "", N23)</f>
         <v>t-dtg-ap-lb-pb8080</v>
       </c>
       <c r="M23" s="86" t="s">
@@ -8230,7 +8253,7 @@
         <v>9087</v>
       </c>
       <c r="L24" s="86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>t-dtg-ap-lb-pb9087</v>
       </c>
       <c r="M24" s="86" t="s">
@@ -8291,7 +8314,7 @@
         <v>8088</v>
       </c>
       <c r="L25" s="84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>t-dtg-admweb-lb-pb8088</v>
       </c>
       <c r="M25" s="84" t="s">
@@ -8352,7 +8375,7 @@
         <v>8085</v>
       </c>
       <c r="L26" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>t-dtg-admap-lb-pb8085</v>
       </c>
       <c r="M26" s="74" t="s">
@@ -8413,7 +8436,7 @@
         <v>8087</v>
       </c>
       <c r="L27" s="74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>t-dtg-admap-lb-pb8087</v>
       </c>
       <c r="M27" s="74" t="s">
@@ -8591,7 +8614,7 @@
         <v>291</v>
       </c>
       <c r="E31" s="74" t="str">
-        <f t="shared" ref="E31:E62" si="6">SUBSTITUTE(D31, "hazr-", "")&amp;"-rule"&amp;N31</f>
+        <f t="shared" ref="E31:E62" si="8">SUBSTITUTE(D31, "hazr-", "")&amp;"-rule"&amp;N31</f>
         <v>t-dis-web-lb-rule80</v>
       </c>
       <c r="F31" s="74" t="str">
@@ -8615,7 +8638,7 @@
         <v>80</v>
       </c>
       <c r="L31" s="74" t="str">
-        <f t="shared" ref="L31:L62" si="7">SUBSTITUTE(D31, "hazr-", "")&amp;"-pb"&amp;IF(N31="", "", N31)</f>
+        <f t="shared" ref="L31:L62" si="9">SUBSTITUTE(D31, "hazr-", "")&amp;"-pb"&amp;IF(N31="", "", N31)</f>
         <v>t-dis-web-lb-pb80</v>
       </c>
       <c r="M31" s="74" t="s">
@@ -8652,7 +8675,7 @@
         <v>291</v>
       </c>
       <c r="E32" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-web-lb-rule443</v>
       </c>
       <c r="F32" s="74" t="str">
@@ -8676,7 +8699,7 @@
         <v>443</v>
       </c>
       <c r="L32" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-web-lb-pb443</v>
       </c>
       <c r="M32" s="74" t="s">
@@ -8713,7 +8736,7 @@
         <v>349</v>
       </c>
       <c r="E33" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-walkweb-lb-rule443</v>
       </c>
       <c r="F33" s="84" t="str">
@@ -8737,7 +8760,7 @@
         <v>443</v>
       </c>
       <c r="L33" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-walkweb-lb-pb443</v>
       </c>
       <c r="M33" s="84" t="s">
@@ -8774,11 +8797,11 @@
         <v>347</v>
       </c>
       <c r="E34" s="86" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-walkap-lb-rule8080</v>
       </c>
       <c r="F34" s="86" t="str">
-        <f t="shared" ref="F34:F64" si="8">SUBSTITUTE(D34, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="F34:F64" si="10">SUBSTITUTE(D34, "hazr-", "")&amp;"-fe"</f>
         <v>t-dis-walkap-lb-fe</v>
       </c>
       <c r="G34" s="86" t="s">
@@ -8791,14 +8814,14 @@
         <v>0</v>
       </c>
       <c r="J34" s="86" t="str">
-        <f t="shared" ref="J34:J64" si="9">SUBSTITUTE(D34, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="J34:J64" si="11">SUBSTITUTE(D34, "hazr-", "")&amp;"-bp"</f>
         <v>t-dis-walkap-lb-bp</v>
       </c>
       <c r="K34" s="86">
         <v>8080</v>
       </c>
       <c r="L34" s="86" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-walkap-lb-pb8080</v>
       </c>
       <c r="M34" s="86" t="s">
@@ -8835,11 +8858,11 @@
         <v>350</v>
       </c>
       <c r="E35" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-drvmsgap-lb-rule8080</v>
       </c>
       <c r="F35" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-drvmsgap-lb-fe</v>
       </c>
       <c r="G35" s="84" t="s">
@@ -8852,14 +8875,14 @@
         <v>0</v>
       </c>
       <c r="J35" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-drvmsgap-lb-bp</v>
       </c>
       <c r="K35" s="84">
         <v>8080</v>
       </c>
       <c r="L35" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-drvmsgap-lb-pb8080</v>
       </c>
       <c r="M35" s="84" t="s">
@@ -8896,11 +8919,11 @@
         <v>348</v>
       </c>
       <c r="E36" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-drvcltap-lb-rule8081</v>
       </c>
       <c r="F36" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-drvcltap-lb-fe</v>
       </c>
       <c r="G36" s="74" t="s">
@@ -8913,14 +8936,14 @@
         <v>0</v>
       </c>
       <c r="J36" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-drvcltap-lb-bp</v>
       </c>
       <c r="K36" s="74">
         <v>8081</v>
       </c>
       <c r="L36" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-drvcltap-lb-pb8081</v>
       </c>
       <c r="M36" s="74" t="s">
@@ -8957,11 +8980,11 @@
         <v>353</v>
       </c>
       <c r="E37" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-cmsweb-lb-rule80</v>
       </c>
       <c r="F37" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
       <c r="G37" s="84" t="s">
@@ -8974,14 +8997,14 @@
         <v>0</v>
       </c>
       <c r="J37" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
       <c r="K37" s="84">
         <v>80</v>
       </c>
       <c r="L37" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-cmsweb-lb-pb80</v>
       </c>
       <c r="M37" s="84" t="s">
@@ -9018,11 +9041,11 @@
         <v>353</v>
       </c>
       <c r="E38" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-cmsweb-lb-rule443</v>
       </c>
       <c r="F38" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
       <c r="G38" s="84" t="s">
@@ -9035,14 +9058,14 @@
         <v>0</v>
       </c>
       <c r="J38" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
       <c r="K38" s="84">
         <v>443</v>
       </c>
       <c r="L38" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-cmsweb-lb-pb443</v>
       </c>
       <c r="M38" s="84" t="s">
@@ -9079,11 +9102,11 @@
         <v>352</v>
       </c>
       <c r="E39" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-cmsap-lb-rule4001</v>
       </c>
       <c r="F39" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-cmsap-lb-fe</v>
       </c>
       <c r="G39" s="74" t="s">
@@ -9096,14 +9119,14 @@
         <v>0</v>
       </c>
       <c r="J39" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-cmsap-lb-bp</v>
       </c>
       <c r="K39" s="74">
         <v>4001</v>
       </c>
       <c r="L39" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-cmsap-lb-pb4001</v>
       </c>
       <c r="M39" s="74" t="s">
@@ -9140,11 +9163,11 @@
         <v>351</v>
       </c>
       <c r="E40" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-cmsadm-lb-rule443</v>
       </c>
       <c r="F40" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-cmsadm-lb-fe</v>
       </c>
       <c r="G40" s="84" t="s">
@@ -9157,14 +9180,14 @@
         <v>0</v>
       </c>
       <c r="J40" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-cmsadm-lb-bp</v>
       </c>
       <c r="K40" s="84">
         <v>443</v>
       </c>
       <c r="L40" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-cmsadm-lb-pb443</v>
       </c>
       <c r="M40" s="84" t="s">
@@ -9201,11 +9224,11 @@
         <v>354</v>
       </c>
       <c r="E41" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-cmbsap-lb-rule8080</v>
       </c>
       <c r="F41" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-cmbsap-lb-fe</v>
       </c>
       <c r="G41" s="74" t="s">
@@ -9218,14 +9241,14 @@
         <v>0</v>
       </c>
       <c r="J41" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-cmbsap-lb-bp</v>
       </c>
       <c r="K41" s="74">
         <v>8080</v>
       </c>
       <c r="L41" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-cmbsap-lb-pb8080</v>
       </c>
       <c r="M41" s="74" t="s">
@@ -9262,11 +9285,11 @@
         <v>344</v>
       </c>
       <c r="E42" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-bbiweb-lb-rule443</v>
       </c>
       <c r="F42" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-bbiweb-lb-fe</v>
       </c>
       <c r="G42" s="84" t="s">
@@ -9279,14 +9302,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-bbiweb-lb-bp</v>
       </c>
       <c r="K42" s="84">
         <v>443</v>
       </c>
       <c r="L42" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-bbiweb-lb-pb443</v>
       </c>
       <c r="M42" s="84" t="s">
@@ -9323,11 +9346,11 @@
         <v>346</v>
       </c>
       <c r="E43" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-bbimsgap-lb-rule20030</v>
       </c>
       <c r="F43" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-bbimsgap-lb-fe</v>
       </c>
       <c r="G43" s="74" t="s">
@@ -9340,14 +9363,14 @@
         <v>0</v>
       </c>
       <c r="J43" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-bbimsgap-lb-bp</v>
       </c>
       <c r="K43" s="74">
         <v>20030</v>
       </c>
       <c r="L43" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-bbimsgap-lb-pb20030</v>
       </c>
       <c r="M43" s="74" t="s">
@@ -9384,11 +9407,11 @@
         <v>345</v>
       </c>
       <c r="E44" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-bbicltap-lb-rule20000</v>
       </c>
       <c r="F44" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
       <c r="G44" s="84" t="s">
@@ -9401,14 +9424,14 @@
         <v>0</v>
       </c>
       <c r="J44" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
       <c r="K44" s="84">
         <v>20000</v>
       </c>
       <c r="L44" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-bbicltap-lb-pb20000</v>
       </c>
       <c r="M44" s="84" t="s">
@@ -9445,11 +9468,11 @@
         <v>345</v>
       </c>
       <c r="E45" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-bbicltap-lb-rule21000</v>
       </c>
       <c r="F45" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
       <c r="G45" s="84" t="s">
@@ -9462,14 +9485,14 @@
         <v>0</v>
       </c>
       <c r="J45" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
       <c r="K45" s="84">
         <v>21000</v>
       </c>
       <c r="L45" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-bbicltap-lb-pb21000</v>
       </c>
       <c r="M45" s="84" t="s">
@@ -9506,11 +9529,11 @@
         <v>345</v>
       </c>
       <c r="E46" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-bbicltap-lb-rule22000</v>
       </c>
       <c r="F46" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
       <c r="G46" s="84" t="s">
@@ -9523,14 +9546,14 @@
         <v>0</v>
       </c>
       <c r="J46" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
       <c r="K46" s="84">
         <v>22000</v>
       </c>
       <c r="L46" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-bbicltap-lb-pb22000</v>
       </c>
       <c r="M46" s="84" t="s">
@@ -9567,11 +9590,11 @@
         <v>289</v>
       </c>
       <c r="E47" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-ap-lb-rule8080</v>
       </c>
       <c r="F47" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-ap-lb-fe</v>
       </c>
       <c r="G47" s="74" t="s">
@@ -9584,14 +9607,14 @@
         <v>0</v>
       </c>
       <c r="J47" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-ap-lb-bp</v>
       </c>
       <c r="K47" s="74">
         <v>8080</v>
       </c>
       <c r="L47" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-ap-lb-pb8080</v>
       </c>
       <c r="M47" s="74" t="s">
@@ -9628,11 +9651,11 @@
         <v>343</v>
       </c>
       <c r="E48" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dis-adm-lb-rule443</v>
       </c>
       <c r="F48" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dis-adm-lb-fe</v>
       </c>
       <c r="G48" s="84" t="s">
@@ -9645,14 +9668,14 @@
         <v>0</v>
       </c>
       <c r="J48" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dis-adm-lb-bp</v>
       </c>
       <c r="K48" s="84">
         <v>443</v>
       </c>
       <c r="L48" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dis-adm-lb-pb443</v>
       </c>
       <c r="M48" s="84" t="s">
@@ -9689,11 +9712,11 @@
         <v>377</v>
       </c>
       <c r="E49" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-web-lb-rule443</v>
       </c>
       <c r="F49" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-web-lb-fe</v>
       </c>
       <c r="G49" s="74" t="s">
@@ -9706,14 +9729,14 @@
         <v>0</v>
       </c>
       <c r="J49" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-web-lb-bp</v>
       </c>
       <c r="K49" s="74">
         <v>443</v>
       </c>
       <c r="L49" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-web-lb-pb443</v>
       </c>
       <c r="M49" s="74" t="s">
@@ -9750,11 +9773,11 @@
         <v>377</v>
       </c>
       <c r="E50" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-web-lb-rule9100</v>
       </c>
       <c r="F50" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-web-lb-fe</v>
       </c>
       <c r="G50" s="74" t="s">
@@ -9767,14 +9790,14 @@
         <v>0</v>
       </c>
       <c r="J50" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-web-lb-bp</v>
       </c>
       <c r="K50" s="74">
         <v>9100</v>
       </c>
       <c r="L50" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-web-lb-pb9100</v>
       </c>
       <c r="M50" s="74" t="s">
@@ -9811,11 +9834,11 @@
         <v>376</v>
       </c>
       <c r="E51" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqweb-lb-rule8883</v>
       </c>
       <c r="F51" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
       <c r="G51" s="84" t="s">
@@ -9828,14 +9851,14 @@
         <v>0</v>
       </c>
       <c r="J51" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
       <c r="K51" s="84">
         <v>8883</v>
       </c>
       <c r="L51" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
       <c r="M51" s="84" t="s">
@@ -9872,11 +9895,11 @@
         <v>376</v>
       </c>
       <c r="E52" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqweb-lb-rule1884</v>
       </c>
       <c r="F52" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
       <c r="G52" s="84" t="s">
@@ -9889,14 +9912,14 @@
         <v>0</v>
       </c>
       <c r="J52" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
       <c r="K52" s="84">
         <v>1884</v>
       </c>
       <c r="L52" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
       <c r="M52" s="84" t="s">
@@ -9933,11 +9956,11 @@
         <v>376</v>
       </c>
       <c r="E53" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqweb-lb-rule9100</v>
       </c>
       <c r="F53" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqweb-lb-fe</v>
       </c>
       <c r="G53" s="84" t="s">
@@ -9950,14 +9973,14 @@
         <v>0</v>
       </c>
       <c r="J53" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqweb-lb-bp</v>
       </c>
       <c r="K53" s="84">
         <v>9100</v>
       </c>
       <c r="L53" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
       <c r="M53" s="84" t="s">
@@ -9994,11 +10017,11 @@
         <v>375</v>
       </c>
       <c r="E54" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqap-lb-rule1883</v>
       </c>
       <c r="F54" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
       <c r="G54" s="74" t="s">
@@ -10011,14 +10034,14 @@
         <v>0</v>
       </c>
       <c r="J54" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqap-lb-bp</v>
       </c>
       <c r="K54" s="74">
         <v>1883</v>
       </c>
       <c r="L54" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
       <c r="M54" s="74" t="s">
@@ -10055,11 +10078,11 @@
         <v>375</v>
       </c>
       <c r="E55" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqap-lb-rule1884</v>
       </c>
       <c r="F55" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
       <c r="G55" s="74" t="s">
@@ -10072,14 +10095,14 @@
         <v>0</v>
       </c>
       <c r="J55" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqap-lb-bp</v>
       </c>
       <c r="K55" s="74">
         <v>1884</v>
       </c>
       <c r="L55" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
       <c r="M55" s="74" t="s">
@@ -10116,11 +10139,11 @@
         <v>375</v>
       </c>
       <c r="E56" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqap-lb-rule18083</v>
       </c>
       <c r="F56" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
       <c r="G56" s="74" t="s">
@@ -10133,14 +10156,14 @@
         <v>0</v>
       </c>
       <c r="J56" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqap-lb-bp</v>
       </c>
       <c r="K56" s="74">
         <v>18083</v>
       </c>
       <c r="L56" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
       <c r="M56" s="74" t="s">
@@ -10177,11 +10200,11 @@
         <v>375</v>
       </c>
       <c r="E57" s="74" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-mqap-lb-rule9100</v>
       </c>
       <c r="F57" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-mqap-lb-fe</v>
       </c>
       <c r="G57" s="74" t="s">
@@ -10194,14 +10217,14 @@
         <v>0</v>
       </c>
       <c r="J57" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-mqap-lb-bp</v>
       </c>
       <c r="K57" s="74">
         <v>9100</v>
       </c>
       <c r="L57" s="74" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-mqap-lb-pb9100</v>
       </c>
       <c r="M57" s="74" t="s">
@@ -10238,11 +10261,11 @@
         <v>374</v>
       </c>
       <c r="E58" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-geoap-lb-rule3660</v>
       </c>
       <c r="F58" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G58" s="84" t="s">
@@ -10255,14 +10278,14 @@
         <v>0</v>
       </c>
       <c r="J58" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K58" s="84">
         <v>3660</v>
       </c>
       <c r="L58" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
       <c r="M58" s="84" t="s">
@@ -10299,11 +10322,11 @@
         <v>374</v>
       </c>
       <c r="E59" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-geoap-lb-rule3661</v>
       </c>
       <c r="F59" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G59" s="84" t="s">
@@ -10316,14 +10339,14 @@
         <v>0</v>
       </c>
       <c r="J59" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K59" s="84">
         <v>3661</v>
       </c>
       <c r="L59" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
       <c r="M59" s="84" t="s">
@@ -10360,11 +10383,11 @@
         <v>374</v>
       </c>
       <c r="E60" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-geoap-lb-rule3670</v>
       </c>
       <c r="F60" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G60" s="84" t="s">
@@ -10377,14 +10400,14 @@
         <v>0</v>
       </c>
       <c r="J60" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K60" s="84">
         <v>3670</v>
       </c>
       <c r="L60" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
       <c r="M60" s="84" t="s">
@@ -10421,11 +10444,11 @@
         <v>374</v>
       </c>
       <c r="E61" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-geoap-lb-rule3671</v>
       </c>
       <c r="F61" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G61" s="84" t="s">
@@ -10438,14 +10461,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K61" s="84">
         <v>3671</v>
       </c>
       <c r="L61" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
       <c r="M61" s="84" t="s">
@@ -10482,11 +10505,11 @@
         <v>374</v>
       </c>
       <c r="E62" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>t-dip-geoap-lb-rule9100</v>
       </c>
       <c r="F62" s="84" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-geoap-lb-fe</v>
       </c>
       <c r="G62" s="84" t="s">
@@ -10499,14 +10522,14 @@
         <v>0</v>
       </c>
       <c r="J62" s="84" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-geoap-lb-bp</v>
       </c>
       <c r="K62" s="84">
         <v>9100</v>
       </c>
       <c r="L62" s="84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
       <c r="M62" s="84" t="s">
@@ -10543,11 +10566,11 @@
         <v>373</v>
       </c>
       <c r="E63" s="74" t="str">
-        <f t="shared" ref="E63:E74" si="10">SUBSTITUTE(D63, "hazr-", "")&amp;"-rule"&amp;N63</f>
+        <f t="shared" ref="E63:E74" si="12">SUBSTITUTE(D63, "hazr-", "")&amp;"-rule"&amp;N63</f>
         <v>t-dip-ap-lb-rule443</v>
       </c>
       <c r="F63" s="74" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G63" s="74" t="s">
@@ -10560,14 +10583,14 @@
         <v>0</v>
       </c>
       <c r="J63" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K63" s="74">
         <v>443</v>
       </c>
       <c r="L63" s="74" t="str">
-        <f t="shared" ref="L63:L74" si="11">SUBSTITUTE(D63, "hazr-", "")&amp;"-pb"&amp;IF(N63="", "", N63)</f>
+        <f t="shared" ref="L63:L74" si="13">SUBSTITUTE(D63, "hazr-", "")&amp;"-pb"&amp;IF(N63="", "", N63)</f>
         <v>t-dip-ap-lb-pb443</v>
       </c>
       <c r="M63" s="74" t="s">
@@ -10604,11 +10627,11 @@
         <v>373</v>
       </c>
       <c r="E64" s="74" t="str">
+        <f t="shared" si="12"/>
+        <v>t-dip-ap-lb-rule8100</v>
+      </c>
+      <c r="F64" s="74" t="str">
         <f t="shared" si="10"/>
-        <v>t-dip-ap-lb-rule8100</v>
-      </c>
-      <c r="F64" s="74" t="str">
-        <f t="shared" si="8"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G64" s="74" t="s">
@@ -10621,14 +10644,14 @@
         <v>0</v>
       </c>
       <c r="J64" s="74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K64" s="74">
         <v>8100</v>
       </c>
       <c r="L64" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
       <c r="M64" s="74" t="s">
@@ -10665,11 +10688,11 @@
         <v>373</v>
       </c>
       <c r="E65" s="74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-ap-lb-rule8200</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F87" si="12">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="F65:F87" si="14">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -10682,14 +10705,14 @@
         <v>0</v>
       </c>
       <c r="J65" s="74" t="str">
-        <f t="shared" ref="J65:J87" si="13">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="J65:J87" si="15">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K65" s="74">
         <v>8200</v>
       </c>
       <c r="L65" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="M65" s="74" t="s">
@@ -10726,11 +10749,11 @@
         <v>373</v>
       </c>
       <c r="E66" s="74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-ap-lb-rule8300</v>
       </c>
       <c r="F66" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G66" s="74" t="s">
@@ -10743,14 +10766,14 @@
         <v>0</v>
       </c>
       <c r="J66" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K66" s="74">
         <v>8300</v>
       </c>
       <c r="L66" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb8300</v>
       </c>
       <c r="M66" s="74" t="s">
@@ -10787,11 +10810,11 @@
         <v>373</v>
       </c>
       <c r="E67" s="74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-ap-lb-rule8400</v>
       </c>
       <c r="F67" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G67" s="74" t="s">
@@ -10804,14 +10827,14 @@
         <v>0</v>
       </c>
       <c r="J67" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K67" s="74">
         <v>8400</v>
       </c>
       <c r="L67" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb8400</v>
       </c>
       <c r="M67" s="74" t="s">
@@ -10848,11 +10871,11 @@
         <v>373</v>
       </c>
       <c r="E68" s="74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-ap-lb-rule9100</v>
       </c>
       <c r="F68" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G68" s="74" t="s">
@@ -10865,14 +10888,14 @@
         <v>0</v>
       </c>
       <c r="J68" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K68" s="74">
         <v>9100</v>
       </c>
       <c r="L68" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb9100</v>
       </c>
       <c r="M68" s="74" t="s">
@@ -10909,11 +10932,11 @@
         <v>373</v>
       </c>
       <c r="E69" s="74" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-ap-lb-rule9113</v>
       </c>
       <c r="F69" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G69" s="74" t="s">
@@ -10926,14 +10949,14 @@
         <v>0</v>
       </c>
       <c r="J69" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K69" s="74">
         <v>9113</v>
       </c>
       <c r="L69" s="74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-ap-lb-pb9113</v>
       </c>
       <c r="M69" s="74" t="s">
@@ -10970,11 +10993,11 @@
         <v>372</v>
       </c>
       <c r="E70" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-adm-lb-rule443</v>
       </c>
       <c r="F70" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-adm-lb-fe</v>
       </c>
       <c r="G70" s="84" t="s">
@@ -10987,14 +11010,14 @@
         <v>0</v>
       </c>
       <c r="J70" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-adm-lb-bp</v>
       </c>
       <c r="K70" s="84">
         <v>443</v>
       </c>
       <c r="L70" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-adm-lb-pb443</v>
       </c>
       <c r="M70" s="84" t="s">
@@ -11031,11 +11054,11 @@
         <v>372</v>
       </c>
       <c r="E71" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-adm-lb-rule8085</v>
       </c>
       <c r="F71" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-adm-lb-fe</v>
       </c>
       <c r="G71" s="84" t="s">
@@ -11048,14 +11071,14 @@
         <v>0</v>
       </c>
       <c r="J71" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-adm-lb-bp</v>
       </c>
       <c r="K71" s="84">
         <v>8085</v>
       </c>
       <c r="L71" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-adm-lb-pb8085</v>
       </c>
       <c r="M71" s="84" t="s">
@@ -11092,11 +11115,11 @@
         <v>372</v>
       </c>
       <c r="E72" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-adm-lb-rule8900</v>
       </c>
       <c r="F72" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-adm-lb-fe</v>
       </c>
       <c r="G72" s="84" t="s">
@@ -11109,14 +11132,14 @@
         <v>0</v>
       </c>
       <c r="J72" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-adm-lb-bp</v>
       </c>
       <c r="K72" s="84">
         <v>8900</v>
       </c>
       <c r="L72" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-adm-lb-pb8900</v>
       </c>
       <c r="M72" s="84" t="s">
@@ -11153,11 +11176,11 @@
         <v>372</v>
       </c>
       <c r="E73" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-adm-lb-rule8901</v>
       </c>
       <c r="F73" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-adm-lb-fe</v>
       </c>
       <c r="G73" s="84" t="s">
@@ -11170,14 +11193,14 @@
         <v>0</v>
       </c>
       <c r="J73" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-adm-lb-bp</v>
       </c>
       <c r="K73" s="84">
         <v>8901</v>
       </c>
       <c r="L73" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-adm-lb-pb8901</v>
       </c>
       <c r="M73" s="84" t="s">
@@ -11214,11 +11237,11 @@
         <v>372</v>
       </c>
       <c r="E74" s="84" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>t-dip-adm-lb-rule9100</v>
       </c>
       <c r="F74" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-dip-adm-lb-fe</v>
       </c>
       <c r="G74" s="84" t="s">
@@ -11231,14 +11254,14 @@
         <v>0</v>
       </c>
       <c r="J74" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-dip-adm-lb-bp</v>
       </c>
       <c r="K74" s="84">
         <v>9100</v>
       </c>
       <c r="L74" s="84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>t-dip-adm-lb-pb9100</v>
       </c>
       <c r="M74" s="84" t="s">
@@ -11276,7 +11299,7 @@
       </c>
       <c r="E75" s="74"/>
       <c r="F75" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-cs-chtweb-lb-fe</v>
       </c>
       <c r="G75" s="74" t="s">
@@ -11287,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-cs-chtweb-lb-bp</v>
       </c>
       <c r="K75" s="74"/>
@@ -11323,7 +11346,7 @@
       </c>
       <c r="E76" s="84"/>
       <c r="F76" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-cs-chtintweb-lb-fe</v>
       </c>
       <c r="G76" s="84" t="s">
@@ -11334,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-cs-chtintweb-lb-bp</v>
       </c>
       <c r="K76" s="84"/>
@@ -11370,7 +11393,7 @@
       </c>
       <c r="E77" s="74"/>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-cs-chtap-lb-fe</v>
       </c>
       <c r="G77" s="74" t="s">
@@ -11381,7 +11404,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-cs-chtap-lb-bp</v>
       </c>
       <c r="K77" s="74"/>
@@ -11416,11 +11439,11 @@
         <v>379</v>
       </c>
       <c r="E78" s="84" t="str">
-        <f t="shared" ref="E78:E87" si="14">SUBSTITUTE(D78, "hazr-", "")&amp;"-rule"&amp;N78</f>
+        <f t="shared" ref="E78:E87" si="16">SUBSTITUTE(D78, "hazr-", "")&amp;"-rule"&amp;N78</f>
         <v>t-com-proxy-lb-rule443</v>
       </c>
       <c r="F78" s="84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>t-com-proxy-lb-fe</v>
       </c>
       <c r="G78" s="84" t="s">
@@ -11433,14 +11456,14 @@
         <v>0</v>
       </c>
       <c r="J78" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-com-proxy-lb-bp</v>
       </c>
       <c r="K78" s="84">
         <v>443</v>
       </c>
       <c r="L78" s="84" t="str">
-        <f t="shared" ref="L78:L87" si="15">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
+        <f t="shared" ref="L78:L87" si="17">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
         <v>t-com-proxy-lb-pb443</v>
       </c>
       <c r="M78" s="84" t="s">
@@ -11477,11 +11500,11 @@
         <v>379</v>
       </c>
       <c r="E79" s="84" t="str">
+        <f t="shared" si="16"/>
+        <v>t-com-proxy-lb-rule8080</v>
+      </c>
+      <c r="F79" s="84" t="str">
         <f t="shared" si="14"/>
-        <v>t-com-proxy-lb-rule8080</v>
-      </c>
-      <c r="F79" s="84" t="str">
-        <f t="shared" si="12"/>
         <v>t-com-proxy-lb-fe</v>
       </c>
       <c r="G79" s="84" t="s">
@@ -11494,14 +11517,14 @@
         <v>0</v>
       </c>
       <c r="J79" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-com-proxy-lb-bp</v>
       </c>
       <c r="K79" s="84">
         <v>8080</v>
       </c>
       <c r="L79" s="84" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-com-proxy-lb-pb8080</v>
       </c>
       <c r="M79" s="84" t="s">
@@ -11538,11 +11561,11 @@
         <v>378</v>
       </c>
       <c r="E80" s="74" t="str">
+        <f t="shared" si="16"/>
+        <v>t-com-auth-lb-rule8088</v>
+      </c>
+      <c r="F80" s="74" t="str">
         <f t="shared" si="14"/>
-        <v>t-com-auth-lb-rule8088</v>
-      </c>
-      <c r="F80" s="74" t="str">
-        <f t="shared" si="12"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G80" s="74" t="s">
@@ -11555,14 +11578,14 @@
         <v>0</v>
       </c>
       <c r="J80" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K80" s="74">
         <v>8088</v>
       </c>
       <c r="L80" s="74" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-com-auth-lb-pb8088</v>
       </c>
       <c r="M80" s="74" t="s">
@@ -11599,11 +11622,11 @@
         <v>378</v>
       </c>
       <c r="E81" s="74" t="str">
+        <f t="shared" si="16"/>
+        <v>t-com-auth-lb-rule9003</v>
+      </c>
+      <c r="F81" s="74" t="str">
         <f t="shared" si="14"/>
-        <v>t-com-auth-lb-rule9003</v>
-      </c>
-      <c r="F81" s="74" t="str">
-        <f t="shared" si="12"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G81" s="74" t="s">
@@ -11616,14 +11639,14 @@
         <v>0</v>
       </c>
       <c r="J81" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K81" s="74">
         <v>9003</v>
       </c>
       <c r="L81" s="74" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-com-auth-lb-pb9003</v>
       </c>
       <c r="M81" s="74" t="s">
@@ -11660,11 +11683,11 @@
         <v>378</v>
       </c>
       <c r="E82" s="74" t="str">
+        <f t="shared" si="16"/>
+        <v>t-com-auth-lb-rule9005</v>
+      </c>
+      <c r="F82" s="74" t="str">
         <f t="shared" si="14"/>
-        <v>t-com-auth-lb-rule9005</v>
-      </c>
-      <c r="F82" s="74" t="str">
-        <f t="shared" si="12"/>
         <v>t-com-auth-lb-fe</v>
       </c>
       <c r="G82" s="74" t="s">
@@ -11677,14 +11700,14 @@
         <v>0</v>
       </c>
       <c r="J82" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-com-auth-lb-bp</v>
       </c>
       <c r="K82" s="74">
         <v>9005</v>
       </c>
       <c r="L82" s="74" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-com-auth-lb-pb9005</v>
       </c>
       <c r="M82" s="74" t="s">
@@ -11721,11 +11744,11 @@
         <v>371</v>
       </c>
       <c r="E83" s="84" t="str">
+        <f t="shared" si="16"/>
+        <v>t-bdp-slap-lb-rule443</v>
+      </c>
+      <c r="F83" s="84" t="str">
         <f t="shared" si="14"/>
-        <v>t-bdp-slap-lb-rule443</v>
-      </c>
-      <c r="F83" s="84" t="str">
-        <f t="shared" si="12"/>
         <v>t-bdp-slap-lb-fe</v>
       </c>
       <c r="G83" s="84" t="s">
@@ -11738,14 +11761,14 @@
         <v>0</v>
       </c>
       <c r="J83" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-bdp-slap-lb-bp</v>
       </c>
       <c r="K83" s="84">
         <v>443</v>
       </c>
       <c r="L83" s="84" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-bdp-slap-lb-pb443</v>
       </c>
       <c r="M83" s="84" t="s">
@@ -11782,11 +11805,11 @@
         <v>370</v>
       </c>
       <c r="E84" s="74" t="str">
+        <f t="shared" si="16"/>
+        <v>t-bdp-cxmadm-lb-rule443</v>
+      </c>
+      <c r="F84" s="74" t="str">
         <f t="shared" si="14"/>
-        <v>t-bdp-cxmadm-lb-rule443</v>
-      </c>
-      <c r="F84" s="74" t="str">
-        <f t="shared" si="12"/>
         <v>t-bdp-cxmadm-lb-fe</v>
       </c>
       <c r="G84" s="74" t="s">
@@ -11799,14 +11822,14 @@
         <v>0</v>
       </c>
       <c r="J84" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-bdp-cxmadm-lb-bp</v>
       </c>
       <c r="K84" s="74">
         <v>443</v>
       </c>
       <c r="L84" s="74" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-bdp-cxmadm-lb-pb443</v>
       </c>
       <c r="M84" s="74" t="s">
@@ -11843,11 +11866,11 @@
         <v>386</v>
       </c>
       <c r="E85" s="84" t="str">
+        <f t="shared" si="16"/>
+        <v>t-bdp-crkweb-lb-rule443</v>
+      </c>
+      <c r="F85" s="84" t="str">
         <f t="shared" si="14"/>
-        <v>t-bdp-crkweb-lb-rule443</v>
-      </c>
-      <c r="F85" s="84" t="str">
-        <f t="shared" si="12"/>
         <v>t-bdp-crkweb-lb-fe</v>
       </c>
       <c r="G85" s="84" t="s">
@@ -11860,14 +11883,14 @@
         <v>0</v>
       </c>
       <c r="J85" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-bdp-crkweb-lb-bp</v>
       </c>
       <c r="K85" s="84">
         <v>443</v>
       </c>
       <c r="L85" s="84" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-bdp-crkweb-lb-pb443</v>
       </c>
       <c r="M85" s="84" t="s">
@@ -11904,11 +11927,11 @@
         <v>388</v>
       </c>
       <c r="E86" s="74" t="str">
+        <f t="shared" si="16"/>
+        <v>t-bdp-crkml-lb-rule8082</v>
+      </c>
+      <c r="F86" s="74" t="str">
         <f t="shared" si="14"/>
-        <v>t-bdp-crkml-lb-rule8082</v>
-      </c>
-      <c r="F86" s="74" t="str">
-        <f t="shared" si="12"/>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="G86" s="74" t="s">
@@ -11921,14 +11944,14 @@
         <v>0</v>
       </c>
       <c r="J86" s="74" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
       <c r="K86" s="74">
         <v>8082</v>
       </c>
       <c r="L86" s="74" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-bdp-crkml-lb-pb8082</v>
       </c>
       <c r="M86" s="74" t="s">
@@ -11965,11 +11988,11 @@
         <v>387</v>
       </c>
       <c r="E87" s="84" t="str">
+        <f t="shared" si="16"/>
+        <v>t-bdp-crkap-lb-rule8085</v>
+      </c>
+      <c r="F87" s="84" t="str">
         <f t="shared" si="14"/>
-        <v>t-bdp-crkap-lb-rule8085</v>
-      </c>
-      <c r="F87" s="84" t="str">
-        <f t="shared" si="12"/>
         <v>t-bdp-crkap-lb-fe</v>
       </c>
       <c r="G87" s="84" t="s">
@@ -11982,14 +12005,14 @@
         <v>0</v>
       </c>
       <c r="J87" s="84" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>t-bdp-crkap-lb-bp</v>
       </c>
       <c r="K87" s="84">
         <v>8085</v>
       </c>
       <c r="L87" s="84" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>t-bdp-crkap-lb-pb8085</v>
       </c>
       <c r="M87" s="84" t="s">
@@ -12223,7 +12246,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF73"/>
+  <dimension ref="A1:AF74"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -13969,7 +13992,7 @@
         <v>288</v>
       </c>
       <c r="E20" s="74" t="s">
-        <v>616</v>
+        <v>24</v>
       </c>
       <c r="F20" s="74" t="s">
         <v>537</v>
@@ -18496,6 +18519,7 @@
       <c r="AF70" s="74"/>
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A71" s="97"/>
       <c r="B71" s="74" t="s">
         <v>615</v>
       </c>
@@ -18584,6 +18608,7 @@
       <c r="AF71" s="74"/>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A72" s="97"/>
       <c r="B72" s="74" t="s">
         <v>615</v>
       </c>
@@ -18672,6 +18697,7 @@
       <c r="AF72" s="74"/>
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A73" s="97"/>
       <c r="B73" s="107" t="s">
         <v>615</v>
       </c>
@@ -18685,10 +18711,10 @@
         <v>24</v>
       </c>
       <c r="F73" s="107" t="s">
+        <v>617</v>
+      </c>
+      <c r="G73" s="107" t="s">
         <v>618</v>
-      </c>
-      <c r="G73" s="107" t="s">
-        <v>619</v>
       </c>
       <c r="H73" s="108" t="s">
         <v>181</v>
@@ -18757,6 +18783,94 @@
       </c>
       <c r="AE73" s="107"/>
       <c r="AF73" s="107"/>
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B74" s="107" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="111" t="str" cm="1">
+        <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($D74, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D74" s="111" t="s">
+        <v>627</v>
+      </c>
+      <c r="E74" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="107" t="s">
+        <v>628</v>
+      </c>
+      <c r="G74" s="107" t="s">
+        <v>630</v>
+      </c>
+      <c r="H74" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="I74" s="107">
+        <v>2</v>
+      </c>
+      <c r="J74" s="107">
+        <v>8</v>
+      </c>
+      <c r="K74" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="L74" s="109" t="s">
+        <v>180</v>
+      </c>
+      <c r="M74" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="N74" s="74" t="s">
+        <v>629</v>
+      </c>
+      <c r="O74" s="111" t="str">
+        <f>SUBSTITUTE(F74,"hazr-","")&amp;"-osdisk"</f>
+        <v>t-if-icsweb01-osdisk</v>
+      </c>
+      <c r="P74" s="107">
+        <v>64</v>
+      </c>
+      <c r="Q74" s="107" t="s">
+        <v>183</v>
+      </c>
+      <c r="R74" s="111"/>
+      <c r="S74" s="107"/>
+      <c r="T74" s="111"/>
+      <c r="U74" s="111" t="str">
+        <f>SUBSTITUTE(F74,"hazr-","")&amp;"-nic"</f>
+        <v>t-if-icsweb01-nic</v>
+      </c>
+      <c r="V74" s="107" t="b">
+        <v>1</v>
+      </c>
+      <c r="W74" s="107" t="b">
+        <v>1</v>
+      </c>
+      <c r="X74" s="107" t="s">
+        <v>497</v>
+      </c>
+      <c r="Y74" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z74" s="107" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA74" s="107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB74" s="107" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC74" s="107" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD74" s="107">
+        <v>3</v>
+      </c>
+      <c r="AE74" s="107"/>
+      <c r="AF74" s="107"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18773,7 +18887,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="75" customWidth="1"/>
@@ -22642,8 +22756,9 @@
       <c r="R70" s="73"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" s="98"/>
       <c r="B71" s="78" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C71" s="74" t="str" cm="1">
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
@@ -22696,8 +22811,9 @@
       <c r="R71" s="74"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A72" s="98"/>
       <c r="B72" s="88" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C72" s="73" t="s">
         <v>610</v>
@@ -22749,8 +22865,9 @@
       <c r="R72" s="73"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A73" s="98"/>
       <c r="B73" s="78" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C73" s="74" t="str" cm="1">
         <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($D73, "-"), 3))</f>
@@ -22763,7 +22880,7 @@
         <v>24</v>
       </c>
       <c r="F73" s="74" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G73" s="74" t="str">
         <f>SUBSTITUTE($F73,"hazr-","")&amp;"-disk01"</f>
@@ -22800,6 +22917,59 @@
         <v>1</v>
       </c>
       <c r="R73" s="74"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B74" s="88" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="73" t="s">
+        <v>631</v>
+      </c>
+      <c r="D74" s="88" t="s">
+        <v>497</v>
+      </c>
+      <c r="E74" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="73" t="s">
+        <v>628</v>
+      </c>
+      <c r="G74" s="73" t="str">
+        <f>SUBSTITUTE($F74,"hazr-","")&amp;"-disk01"</f>
+        <v>t-if-icsweb01-disk01</v>
+      </c>
+      <c r="H74" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="I74" s="73">
+        <v>128</v>
+      </c>
+      <c r="J74" s="73" t="str">
+        <f>SUBSTITUTE($F74,"hazr-","")&amp;"-disk02"</f>
+        <v>t-if-icsweb01-disk02</v>
+      </c>
+      <c r="K74" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="L74" s="73">
+        <v>128</v>
+      </c>
+      <c r="M74" s="73">
+        <v>3</v>
+      </c>
+      <c r="N74" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="O74" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="P74" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q74" s="73" t="b">
+        <v>1</v>
+      </c>
+      <c r="R74" s="73"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -22812,7 +22982,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5" customWidth="1"/>
@@ -26220,7 +26390,7 @@
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="110"/>
       <c r="B89" s="82" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C89" s="82" t="str" cm="1">
         <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($D89, "-"), 3))</f>
@@ -26255,13 +26425,13 @@
         <v>593</v>
       </c>
       <c r="M89" s="74" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="110"/>
       <c r="B90" s="80" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C90" s="80" t="str" cm="1">
         <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($D90, "-"), 3))</f>
@@ -26296,13 +26466,13 @@
         <v>593</v>
       </c>
       <c r="M90" s="73" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="110"/>
       <c r="B91" s="82" t="s">
-        <v>23</v>
+        <v>615</v>
       </c>
       <c r="C91" s="82" t="str" cm="1">
         <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($D91, "-"), 3))</f>
@@ -26325,19 +26495,59 @@
         <v>606</v>
       </c>
       <c r="I91" s="74" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J91" s="74" t="s">
         <v>601</v>
       </c>
       <c r="K91" s="74" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L91" s="74" t="s">
         <v>593</v>
       </c>
       <c r="M91" s="74" t="s">
-        <v>621</v>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B92" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" s="80" t="s">
+        <v>631</v>
+      </c>
+      <c r="D92" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="E92" s="80" t="str">
+        <f>SUBSTITUTE(I92,"hazr-","")&amp;"-nsg"</f>
+        <v>t-if-icsweb01-nsg</v>
+      </c>
+      <c r="F92" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="G92" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="H92" s="73" t="s">
+        <v>340</v>
+      </c>
+      <c r="I92" s="73" t="s">
+        <v>628</v>
+      </c>
+      <c r="J92" s="73" t="s">
+        <v>497</v>
+      </c>
+      <c r="K92" s="73" t="str">
+        <f>SUBSTITUTE(I92,"hazr-","")&amp;"-nic"</f>
+        <v>t-if-icsweb01-nic</v>
+      </c>
+      <c r="L92" s="73" t="s">
+        <v>593</v>
+      </c>
+      <c r="M92" s="73" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -31900,7 +32110,7 @@
         <v>8080</v>
       </c>
       <c r="I14" s="86" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J14" s="86">
         <v>5</v>
@@ -32075,6 +32285,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="97"/>
       <c r="B20" s="86" t="s">
         <v>184</v>
       </c>
@@ -32090,10 +32301,14 @@
       </c>
       <c r="F20" s="86" t="str">
         <f t="shared" si="0"/>
-        <v>t-dtg-cdstap-lb-pb</v>
-      </c>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
+        <v>t-dtg-cdstap-lb-pb9305</v>
+      </c>
+      <c r="G20" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="74">
+        <v>9305</v>
+      </c>
       <c r="I20" s="86"/>
       <c r="J20" s="86">
         <v>5</v>
@@ -32104,39 +32319,38 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="97"/>
-      <c r="B21" s="84" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="84" t="str" cm="1">
+      <c r="B21" s="86" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="86" t="str" cm="1">
         <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D21" s="84" t="s">
+      <c r="D21" s="86" t="s">
         <v>389</v>
       </c>
-      <c r="E21" s="84" t="s">
-        <v>363</v>
-      </c>
-      <c r="F21" s="84" t="str">
-        <f t="shared" si="0"/>
-        <v>t-dtg-cdmlap-lb-pb9305</v>
-      </c>
-      <c r="G21" s="84" t="s">
+      <c r="E21" s="86" t="s">
+        <v>364</v>
+      </c>
+      <c r="F21" s="86" t="str">
+        <f t="shared" ref="F21" si="1">SUBSTITUTE(E21, "hazr-", "")&amp;"-pb"&amp;H21</f>
+        <v>t-dtg-cdstap-lb-pb9306</v>
+      </c>
+      <c r="G21" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="84">
-        <v>9305</v>
-      </c>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84">
+      <c r="H21" s="74">
+        <v>9306</v>
+      </c>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86">
         <v>5</v>
       </c>
-      <c r="K21" s="84">
+      <c r="K21" s="86">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="97"/>
       <c r="B22" s="84" t="s">
         <v>184</v>
       </c>
@@ -32152,14 +32366,10 @@
       </c>
       <c r="F22" s="84" t="str">
         <f t="shared" si="0"/>
-        <v>t-dtg-cdmlap-lb-pb9306</v>
-      </c>
-      <c r="G22" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="84">
-        <v>9306</v>
-      </c>
+        <v>t-dtg-cdmlap-lb-pb</v>
+      </c>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
       <c r="I22" s="84"/>
       <c r="J22" s="84">
         <v>5</v>
@@ -32531,7 +32741,7 @@
         <v>347</v>
       </c>
       <c r="F34" s="86" t="str">
-        <f t="shared" ref="F34:F64" si="1">SUBSTITUTE(E34, "hazr-", "")&amp;"-pb"&amp;H34</f>
+        <f t="shared" ref="F34:F64" si="2">SUBSTITUTE(E34, "hazr-", "")&amp;"-pb"&amp;H34</f>
         <v>t-dis-walkap-lb-pb8080</v>
       </c>
       <c r="G34" s="86" t="s">
@@ -32541,7 +32751,7 @@
         <v>8080</v>
       </c>
       <c r="I34" s="86" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J34" s="86">
         <v>5</v>
@@ -32566,7 +32776,7 @@
         <v>350</v>
       </c>
       <c r="F35" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-drvmsgap-lb-pb8080</v>
       </c>
       <c r="G35" s="84" t="s">
@@ -32576,7 +32786,7 @@
         <v>8080</v>
       </c>
       <c r="I35" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J35" s="84">
         <v>5</v>
@@ -32601,7 +32811,7 @@
         <v>348</v>
       </c>
       <c r="F36" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-drvcltap-lb-pb8081</v>
       </c>
       <c r="G36" s="74" t="s">
@@ -32636,7 +32846,7 @@
         <v>353</v>
       </c>
       <c r="F37" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-cmsweb-lb-pb80</v>
       </c>
       <c r="G37" s="84" t="s">
@@ -32669,7 +32879,7 @@
         <v>353</v>
       </c>
       <c r="F38" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-cmsweb-lb-pb443</v>
       </c>
       <c r="G38" s="84" t="s">
@@ -32702,7 +32912,7 @@
         <v>352</v>
       </c>
       <c r="F39" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-cmsap-lb-pb4001</v>
       </c>
       <c r="G39" s="74" t="s">
@@ -32735,7 +32945,7 @@
         <v>351</v>
       </c>
       <c r="F40" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-cmsadm-lb-pb443</v>
       </c>
       <c r="G40" s="84" t="s">
@@ -32768,7 +32978,7 @@
         <v>354</v>
       </c>
       <c r="F41" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-cmbsap-lb-pb8080</v>
       </c>
       <c r="G41" s="74" t="s">
@@ -32778,7 +32988,7 @@
         <v>8080</v>
       </c>
       <c r="I41" s="74" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J41" s="74">
         <v>5</v>
@@ -32803,7 +33013,7 @@
         <v>344</v>
       </c>
       <c r="F42" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-bbiweb-lb-pb443</v>
       </c>
       <c r="G42" s="84" t="s">
@@ -32836,7 +33046,7 @@
         <v>346</v>
       </c>
       <c r="F43" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-bbimsgap-lb-pb20030</v>
       </c>
       <c r="G43" s="74" t="s">
@@ -32846,7 +33056,7 @@
         <v>20030</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J43" s="74">
         <v>5</v>
@@ -32871,7 +33081,7 @@
         <v>345</v>
       </c>
       <c r="F44" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-pb20000</v>
       </c>
       <c r="G44" s="84" t="s">
@@ -32881,7 +33091,7 @@
         <v>20000</v>
       </c>
       <c r="I44" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J44" s="84">
         <v>5</v>
@@ -32906,7 +33116,7 @@
         <v>345</v>
       </c>
       <c r="F45" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-pb21000</v>
       </c>
       <c r="G45" s="84" t="s">
@@ -32916,7 +33126,7 @@
         <v>21000</v>
       </c>
       <c r="I45" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J45" s="84">
         <v>5</v>
@@ -32941,7 +33151,7 @@
         <v>345</v>
       </c>
       <c r="F46" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-bbicltap-lb-pb22000</v>
       </c>
       <c r="G46" s="84" t="s">
@@ -32951,7 +33161,7 @@
         <v>22000</v>
       </c>
       <c r="I46" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J46" s="84">
         <v>5</v>
@@ -32975,7 +33185,7 @@
         <v>289</v>
       </c>
       <c r="F47" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-ap-lb-pb8080</v>
       </c>
       <c r="G47" s="74" t="s">
@@ -33007,7 +33217,7 @@
         <v>343</v>
       </c>
       <c r="F48" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dis-adm-lb-pb443</v>
       </c>
       <c r="G48" s="84" t="s">
@@ -33040,7 +33250,7 @@
         <v>377</v>
       </c>
       <c r="F49" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-web-lb-pb443</v>
       </c>
       <c r="G49" s="74" t="s">
@@ -33050,7 +33260,7 @@
         <v>443</v>
       </c>
       <c r="I49" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J49" s="74">
         <v>5</v>
@@ -33075,7 +33285,7 @@
         <v>377</v>
       </c>
       <c r="F50" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-web-lb-pb9100</v>
       </c>
       <c r="G50" s="74" t="s">
@@ -33085,7 +33295,7 @@
         <v>9100</v>
       </c>
       <c r="I50" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J50" s="74">
         <v>5</v>
@@ -33110,7 +33320,7 @@
         <v>376</v>
       </c>
       <c r="F51" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb8883</v>
       </c>
       <c r="G51" s="84" t="s">
@@ -33120,7 +33330,7 @@
         <v>8883</v>
       </c>
       <c r="I51" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J51" s="84">
         <v>5</v>
@@ -33145,7 +33355,7 @@
         <v>376</v>
       </c>
       <c r="F52" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb1884</v>
       </c>
       <c r="G52" s="84" t="s">
@@ -33155,7 +33365,7 @@
         <v>1884</v>
       </c>
       <c r="I52" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J52" s="84">
         <v>5</v>
@@ -33180,7 +33390,7 @@
         <v>376</v>
       </c>
       <c r="F53" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqweb-lb-pb9100</v>
       </c>
       <c r="G53" s="84" t="s">
@@ -33190,7 +33400,7 @@
         <v>9100</v>
       </c>
       <c r="I53" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J53" s="84">
         <v>5</v>
@@ -33215,7 +33425,7 @@
         <v>375</v>
       </c>
       <c r="F54" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb1883</v>
       </c>
       <c r="G54" s="74" t="s">
@@ -33225,7 +33435,7 @@
         <v>1883</v>
       </c>
       <c r="I54" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J54" s="74">
         <v>5</v>
@@ -33250,7 +33460,7 @@
         <v>375</v>
       </c>
       <c r="F55" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb1884</v>
       </c>
       <c r="G55" s="74" t="s">
@@ -33260,7 +33470,7 @@
         <v>1884</v>
       </c>
       <c r="I55" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J55" s="74">
         <v>5</v>
@@ -33285,7 +33495,7 @@
         <v>375</v>
       </c>
       <c r="F56" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb18083</v>
       </c>
       <c r="G56" s="74" t="s">
@@ -33295,7 +33505,7 @@
         <v>18083</v>
       </c>
       <c r="I56" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J56" s="74">
         <v>5</v>
@@ -33320,7 +33530,7 @@
         <v>375</v>
       </c>
       <c r="F57" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-mqap-lb-pb9100</v>
       </c>
       <c r="G57" s="74" t="s">
@@ -33330,7 +33540,7 @@
         <v>9100</v>
       </c>
       <c r="I57" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J57" s="74">
         <v>5</v>
@@ -33355,7 +33565,7 @@
         <v>374</v>
       </c>
       <c r="F58" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3660</v>
       </c>
       <c r="G58" s="84" t="s">
@@ -33365,7 +33575,7 @@
         <v>3660</v>
       </c>
       <c r="I58" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J58" s="84">
         <v>5</v>
@@ -33390,7 +33600,7 @@
         <v>374</v>
       </c>
       <c r="F59" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3661</v>
       </c>
       <c r="G59" s="84" t="s">
@@ -33400,7 +33610,7 @@
         <v>3661</v>
       </c>
       <c r="I59" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J59" s="84">
         <v>5</v>
@@ -33425,7 +33635,7 @@
         <v>374</v>
       </c>
       <c r="F60" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3670</v>
       </c>
       <c r="G60" s="84" t="s">
@@ -33435,7 +33645,7 @@
         <v>3670</v>
       </c>
       <c r="I60" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J60" s="84">
         <v>5</v>
@@ -33460,7 +33670,7 @@
         <v>374</v>
       </c>
       <c r="F61" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb3671</v>
       </c>
       <c r="G61" s="84" t="s">
@@ -33470,7 +33680,7 @@
         <v>3671</v>
       </c>
       <c r="I61" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J61" s="84">
         <v>5</v>
@@ -33495,7 +33705,7 @@
         <v>374</v>
       </c>
       <c r="F62" s="84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-geoap-lb-pb9100</v>
       </c>
       <c r="G62" s="84" t="s">
@@ -33505,7 +33715,7 @@
         <v>9100</v>
       </c>
       <c r="I62" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J62" s="84">
         <v>5</v>
@@ -33530,7 +33740,7 @@
         <v>373</v>
       </c>
       <c r="F63" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb443</v>
       </c>
       <c r="G63" s="74" t="s">
@@ -33540,7 +33750,7 @@
         <v>443</v>
       </c>
       <c r="I63" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J63" s="74">
         <v>5</v>
@@ -33565,7 +33775,7 @@
         <v>373</v>
       </c>
       <c r="F64" s="74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>t-dip-ap-lb-pb8100</v>
       </c>
       <c r="G64" s="74" t="s">
@@ -33575,7 +33785,7 @@
         <v>8100</v>
       </c>
       <c r="I64" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J64" s="74">
         <v>5</v>
@@ -33600,7 +33810,7 @@
         <v>373</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F87" si="2">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
+        <f t="shared" ref="F65:F87" si="3">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -33610,7 +33820,7 @@
         <v>8200</v>
       </c>
       <c r="I65" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J65" s="74">
         <v>5</v>
@@ -33635,7 +33845,7 @@
         <v>373</v>
       </c>
       <c r="F66" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-ap-lb-pb8300</v>
       </c>
       <c r="G66" s="74" t="s">
@@ -33645,7 +33855,7 @@
         <v>8300</v>
       </c>
       <c r="I66" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J66" s="74">
         <v>5</v>
@@ -33670,7 +33880,7 @@
         <v>373</v>
       </c>
       <c r="F67" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-ap-lb-pb8400</v>
       </c>
       <c r="G67" s="74" t="s">
@@ -33680,7 +33890,7 @@
         <v>8400</v>
       </c>
       <c r="I67" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J67" s="74">
         <v>5</v>
@@ -33705,7 +33915,7 @@
         <v>373</v>
       </c>
       <c r="F68" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-ap-lb-pb9100</v>
       </c>
       <c r="G68" s="74" t="s">
@@ -33715,7 +33925,7 @@
         <v>9100</v>
       </c>
       <c r="I68" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J68" s="74">
         <v>5</v>
@@ -33740,7 +33950,7 @@
         <v>373</v>
       </c>
       <c r="F69" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-ap-lb-pb9113</v>
       </c>
       <c r="G69" s="74" t="s">
@@ -33750,7 +33960,7 @@
         <v>9113</v>
       </c>
       <c r="I69" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J69" s="74">
         <v>5</v>
@@ -33775,7 +33985,7 @@
         <v>372</v>
       </c>
       <c r="F70" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-adm-lb-pb443</v>
       </c>
       <c r="G70" s="84" t="s">
@@ -33785,7 +33995,7 @@
         <v>443</v>
       </c>
       <c r="I70" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J70" s="84">
         <v>5</v>
@@ -33810,7 +34020,7 @@
         <v>372</v>
       </c>
       <c r="F71" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-adm-lb-pb8085</v>
       </c>
       <c r="G71" s="84" t="s">
@@ -33820,7 +34030,7 @@
         <v>8085</v>
       </c>
       <c r="I71" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J71" s="84">
         <v>5</v>
@@ -33845,7 +34055,7 @@
         <v>372</v>
       </c>
       <c r="F72" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-adm-lb-pb8900</v>
       </c>
       <c r="G72" s="84" t="s">
@@ -33855,7 +34065,7 @@
         <v>8900</v>
       </c>
       <c r="I72" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J72" s="84">
         <v>5</v>
@@ -33880,7 +34090,7 @@
         <v>372</v>
       </c>
       <c r="F73" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-adm-lb-pb8901</v>
       </c>
       <c r="G73" s="84" t="s">
@@ -33890,7 +34100,7 @@
         <v>8901</v>
       </c>
       <c r="I73" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J73" s="84">
         <v>5</v>
@@ -33915,7 +34125,7 @@
         <v>372</v>
       </c>
       <c r="F74" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-dip-adm-lb-pb9100</v>
       </c>
       <c r="G74" s="84" t="s">
@@ -33925,7 +34135,7 @@
         <v>9100</v>
       </c>
       <c r="I74" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J74" s="84">
         <v>5</v>
@@ -33949,7 +34159,7 @@
         <v>381</v>
       </c>
       <c r="F75" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-cs-chtweb-lb-pb</v>
       </c>
       <c r="G75" s="74"/>
@@ -33977,7 +34187,7 @@
         <v>382</v>
       </c>
       <c r="F76" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-cs-chtintweb-lb-pb</v>
       </c>
       <c r="G76" s="84"/>
@@ -34005,7 +34215,7 @@
         <v>380</v>
       </c>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-cs-chtap-lb-pb</v>
       </c>
       <c r="G77" s="74"/>
@@ -34034,7 +34244,7 @@
         <v>379</v>
       </c>
       <c r="F78" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-com-proxy-lb-pb443</v>
       </c>
       <c r="G78" s="84" t="s">
@@ -34044,7 +34254,7 @@
         <v>443</v>
       </c>
       <c r="I78" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J78" s="84">
         <v>5</v>
@@ -34069,7 +34279,7 @@
         <v>379</v>
       </c>
       <c r="F79" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-com-proxy-lb-pb8080</v>
       </c>
       <c r="G79" s="84" t="s">
@@ -34079,7 +34289,7 @@
         <v>8080</v>
       </c>
       <c r="I79" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J79" s="84">
         <v>5</v>
@@ -34104,18 +34314,16 @@
         <v>378</v>
       </c>
       <c r="F80" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-com-auth-lb-pb8088</v>
       </c>
       <c r="G80" s="74" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H80" s="74">
         <v>8088</v>
       </c>
-      <c r="I80" s="74" t="s">
-        <v>623</v>
-      </c>
+      <c r="I80" s="74"/>
       <c r="J80" s="74">
         <v>5</v>
       </c>
@@ -34139,18 +34347,16 @@
         <v>378</v>
       </c>
       <c r="F81" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-com-auth-lb-pb9003</v>
       </c>
       <c r="G81" s="74" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H81" s="74">
         <v>9003</v>
       </c>
-      <c r="I81" s="74" t="s">
-        <v>623</v>
-      </c>
+      <c r="I81" s="74"/>
       <c r="J81" s="74">
         <v>5</v>
       </c>
@@ -34174,18 +34380,16 @@
         <v>378</v>
       </c>
       <c r="F82" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-com-auth-lb-pb9005</v>
       </c>
       <c r="G82" s="74" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H82" s="74">
         <v>9005</v>
       </c>
-      <c r="I82" s="74" t="s">
-        <v>623</v>
-      </c>
+      <c r="I82" s="74"/>
       <c r="J82" s="74">
         <v>5</v>
       </c>
@@ -34209,7 +34413,7 @@
         <v>371</v>
       </c>
       <c r="F83" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-bdp-slap-lb-pb443</v>
       </c>
       <c r="G83" s="84" t="s">
@@ -34219,7 +34423,7 @@
         <v>443</v>
       </c>
       <c r="I83" s="84" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J83" s="84">
         <v>5</v>
@@ -34244,7 +34448,7 @@
         <v>370</v>
       </c>
       <c r="F84" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-bdp-cxmadm-lb-pb443</v>
       </c>
       <c r="G84" s="74" t="s">
@@ -34254,7 +34458,7 @@
         <v>443</v>
       </c>
       <c r="I84" s="74" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J84" s="74">
         <v>5</v>
@@ -34278,7 +34482,7 @@
         <v>386</v>
       </c>
       <c r="F85" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-bdp-crkweb-lb-pb443</v>
       </c>
       <c r="G85" s="84" t="s">
@@ -34310,7 +34514,7 @@
         <v>388</v>
       </c>
       <c r="F86" s="74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-bdp-crkml-lb-pb8082</v>
       </c>
       <c r="G86" s="74" t="s">
@@ -34342,7 +34546,7 @@
         <v>387</v>
       </c>
       <c r="F87" s="84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>t-bdp-crkap-lb-pb8085</v>
       </c>
       <c r="G87" s="84" t="s">
@@ -34366,9 +34570,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34516,26 +34723,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34559,9 +34755,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C8097E-DF50-43F8-99B1-FB574575626A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2DE37F-A684-4F09-AC99-7279A845AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4875" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4875" uniqueCount="632">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3948,10 +3948,6 @@
   </si>
   <si>
     <t>PBProtocol</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-l-if-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4460,7 +4456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4793,9 +4789,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -18788,21 +18781,21 @@
       <c r="B74" s="107" t="s">
         <v>184</v>
       </c>
-      <c r="C74" s="111" t="str" cm="1">
+      <c r="C74" s="107" t="str" cm="1">
         <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($D74, "-"), 3))</f>
         <v>IF</v>
       </c>
-      <c r="D74" s="111" t="s">
-        <v>627</v>
+      <c r="D74" s="107" t="s">
+        <v>497</v>
       </c>
       <c r="E74" s="107" t="s">
         <v>24</v>
       </c>
       <c r="F74" s="107" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G74" s="107" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H74" s="108" t="s">
         <v>181</v>
@@ -18823,9 +18816,9 @@
         <v>602</v>
       </c>
       <c r="N74" s="74" t="s">
-        <v>629</v>
-      </c>
-      <c r="O74" s="111" t="str">
+        <v>628</v>
+      </c>
+      <c r="O74" s="107" t="str">
         <f>SUBSTITUTE(F74,"hazr-","")&amp;"-osdisk"</f>
         <v>t-if-icsweb01-osdisk</v>
       </c>
@@ -18835,10 +18828,10 @@
       <c r="Q74" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="R74" s="111"/>
+      <c r="R74" s="107"/>
       <c r="S74" s="107"/>
-      <c r="T74" s="111"/>
-      <c r="U74" s="111" t="str">
+      <c r="T74" s="107"/>
+      <c r="U74" s="107" t="str">
         <f>SUBSTITUTE(F74,"hazr-","")&amp;"-nic"</f>
         <v>t-if-icsweb01-nic</v>
       </c>
@@ -22923,7 +22916,7 @@
         <v>184</v>
       </c>
       <c r="C74" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D74" s="88" t="s">
         <v>497</v>
@@ -22932,7 +22925,7 @@
         <v>24</v>
       </c>
       <c r="F74" s="73" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G74" s="73" t="str">
         <f>SUBSTITUTE($F74,"hazr-","")&amp;"-disk01"</f>
@@ -26515,7 +26508,7 @@
         <v>184</v>
       </c>
       <c r="C92" s="80" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D92" s="80" t="s">
         <v>200</v>
@@ -26534,7 +26527,7 @@
         <v>340</v>
       </c>
       <c r="I92" s="73" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J92" s="73" t="s">
         <v>497</v>
@@ -26547,7 +26540,7 @@
         <v>593</v>
       </c>
       <c r="M92" s="73" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -34570,12 +34563,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34723,15 +34713,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34755,17 +34756,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2DE37F-A684-4F09-AC99-7279A845AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8497C9C-DB05-4554-973A-2CFF87D74F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18842,7 +18842,7 @@
         <v>1</v>
       </c>
       <c r="X74" s="107" t="s">
-        <v>497</v>
+        <v>200</v>
       </c>
       <c r="Y74" s="107" t="s">
         <v>201</v>
@@ -34563,9 +34563,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34713,26 +34716,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34756,9 +34748,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8497C9C-DB05-4554-973A-2CFF87D74F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A4F72-0D2E-4132-85AE-2059ADAB0F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3955,10 +3955,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10.157.135.10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3968,6 +3964,10 @@
   </si>
   <si>
     <t>6/5 요청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18795,7 +18795,7 @@
         <v>627</v>
       </c>
       <c r="G74" s="107" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H74" s="108" t="s">
         <v>181</v>
@@ -18816,7 +18816,7 @@
         <v>602</v>
       </c>
       <c r="N74" s="74" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="O74" s="107" t="str">
         <f>SUBSTITUTE(F74,"hazr-","")&amp;"-osdisk"</f>
@@ -22916,7 +22916,7 @@
         <v>184</v>
       </c>
       <c r="C74" s="73" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D74" s="88" t="s">
         <v>497</v>
@@ -26508,7 +26508,7 @@
         <v>184</v>
       </c>
       <c r="C92" s="80" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D92" s="80" t="s">
         <v>200</v>
@@ -26540,7 +26540,7 @@
         <v>593</v>
       </c>
       <c r="M92" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>

--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD46242-CE10-4756-9033-F7B4C39A06DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FCE95F-F337-45C7-9E4E-6739B692F0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -3938,10 +3938,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.157.135.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t-if-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3950,10 +3946,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.157.135.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10.157.165.20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3965,6 +3957,14 @@
   </si>
   <si>
     <t>hazr-t-if-auth-lb</t>
+  </si>
+  <si>
+    <t>10.157.135.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.135.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11436,10 +11436,10 @@
         <v>IF</v>
       </c>
       <c r="C78" s="84" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D78" s="84" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E78" s="84" t="str">
         <f t="shared" ref="E78:E87" si="16">SUBSTITUTE(D78, "hazr-", "")&amp;"-rule"&amp;N78</f>
@@ -11497,10 +11497,10 @@
         <v>IF</v>
       </c>
       <c r="C79" s="84" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D79" s="84" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E79" s="84" t="str">
         <f t="shared" si="16"/>
@@ -11558,10 +11558,10 @@
         <v>IF</v>
       </c>
       <c r="C80" s="74" t="s">
+        <v>626</v>
+      </c>
+      <c r="D80" s="74" t="s">
         <v>628</v>
-      </c>
-      <c r="D80" s="74" t="s">
-        <v>630</v>
       </c>
       <c r="E80" s="74" t="str">
         <f t="shared" si="16"/>
@@ -11619,10 +11619,10 @@
         <v>IF</v>
       </c>
       <c r="C81" s="74" t="s">
+        <v>626</v>
+      </c>
+      <c r="D81" s="74" t="s">
         <v>628</v>
-      </c>
-      <c r="D81" s="74" t="s">
-        <v>630</v>
       </c>
       <c r="E81" s="74" t="str">
         <f t="shared" si="16"/>
@@ -11680,10 +11680,10 @@
         <v>IF</v>
       </c>
       <c r="C82" s="74" t="s">
+        <v>626</v>
+      </c>
+      <c r="D82" s="74" t="s">
         <v>628</v>
-      </c>
-      <c r="D82" s="74" t="s">
-        <v>630</v>
       </c>
       <c r="E82" s="74" t="str">
         <f t="shared" si="16"/>
@@ -17828,7 +17828,7 @@
         <v>619</v>
       </c>
       <c r="G63" s="74" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="H63" s="74" t="s">
         <v>576</v>
@@ -29217,13 +29217,13 @@
         <v>201</v>
       </c>
       <c r="N4" s="84" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="O4" s="84" t="s">
         <v>108</v>
       </c>
       <c r="P4" s="84" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="Q4" s="85" t="str">
         <f t="shared" ref="Q4:Q49" si="1">SUBSTITUTE(F4, "hazr-", "")&amp;"-bp"</f>
@@ -31141,13 +31141,13 @@
         <v>200</v>
       </c>
       <c r="N41" s="74" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="O41" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="Q41" s="87" t="str">
         <f t="shared" si="1"/>
@@ -34178,7 +34178,7 @@
         <v>487</v>
       </c>
       <c r="E78" s="84" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F78" s="84" t="str">
         <f t="shared" si="3"/>
@@ -34211,7 +34211,7 @@
         <v>487</v>
       </c>
       <c r="E79" s="84" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F79" s="84" t="str">
         <f t="shared" si="3"/>
@@ -34244,7 +34244,7 @@
         <v>487</v>
       </c>
       <c r="E80" s="74" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F80" s="74" t="str">
         <f t="shared" si="3"/>
@@ -34277,7 +34277,7 @@
         <v>487</v>
       </c>
       <c r="E81" s="74" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F81" s="74" t="str">
         <f t="shared" si="3"/>
@@ -34310,7 +34310,7 @@
         <v>487</v>
       </c>
       <c r="E82" s="74" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F82" s="74" t="str">
         <f t="shared" si="3"/>
@@ -34499,21 +34499,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34657,10 +34642,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34682,19 +34692,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FCE95F-F337-45C7-9E4E-6739B692F0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC0F61B-70A0-42CC-8E41-CAF3B017CDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4836" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4837" uniqueCount="632">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3964,6 +3964,10 @@
   </si>
   <si>
     <t>10.157.135.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -26386,7 +26390,9 @@
       </c>
       <c r="I88" s="73"/>
       <c r="J88" s="73"/>
-      <c r="K88" s="73"/>
+      <c r="K88" s="73" t="s">
+        <v>631</v>
+      </c>
       <c r="L88" s="73" t="s">
         <v>585</v>
       </c>
@@ -34499,6 +34505,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34642,35 +34663,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34692,9 +34688,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6A43DC-C933-4E62-9DDB-F2A979F96936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C68D1B-E5D6-45FB-A91A-A4A92D0FC548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4821" uniqueCount="635">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3956,6 +3956,30 @@
   </si>
   <si>
     <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-com-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-com-auth-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-com-ap-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.165.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -29078,7 +29102,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="74" t="str">
-        <f>SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="K2:K44" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="L2" s="74" t="s">
@@ -29097,7 +29121,7 @@
         <v>480</v>
       </c>
       <c r="Q2" s="87" t="str">
-        <f>SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="Q2:Q44" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
     </row>
@@ -29132,7 +29156,7 @@
         <v>102</v>
       </c>
       <c r="K3" s="84" t="str">
-        <f>SUBSTITUTE(F3, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-bdp-crkap-lb-fe</v>
       </c>
       <c r="L3" s="84" t="s">
@@ -29151,7 +29175,7 @@
         <v>479</v>
       </c>
       <c r="Q3" s="85" t="str">
-        <f>SUBSTITUTE(F3, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-bdp-crkap-lb-bp</v>
       </c>
     </row>
@@ -29186,7 +29210,7 @@
         <v>102</v>
       </c>
       <c r="K4" s="74" t="str">
-        <f>SUBSTITUTE(F4, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-bdp-slap-lb-fe</v>
       </c>
       <c r="L4" s="74" t="s">
@@ -29205,7 +29229,7 @@
         <v>471</v>
       </c>
       <c r="Q4" s="87" t="str">
-        <f>SUBSTITUTE(F4, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-bdp-slap-lb-bp</v>
       </c>
     </row>
@@ -29240,7 +29264,7 @@
         <v>102</v>
       </c>
       <c r="K5" s="84" t="str">
-        <f>SUBSTITUTE(F5, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-bdp-cxmadm-lb-fe</v>
       </c>
       <c r="L5" s="84" t="s">
@@ -29259,7 +29283,7 @@
         <v>470</v>
       </c>
       <c r="Q5" s="85" t="str">
-        <f>SUBSTITUTE(F5, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-bdp-cxmadm-lb-bp</v>
       </c>
     </row>
@@ -29294,7 +29318,7 @@
         <v>102</v>
       </c>
       <c r="K6" s="84" t="str">
-        <f>SUBSTITUTE(F6, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-bdp-crkweb-lb-fe</v>
       </c>
       <c r="L6" s="84" t="s">
@@ -29313,7 +29337,7 @@
         <v>478</v>
       </c>
       <c r="Q6" s="85" t="str">
-        <f>SUBSTITUTE(F6, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-bdp-crkweb-lb-bp</v>
       </c>
     </row>
@@ -29348,7 +29372,7 @@
         <v>102</v>
       </c>
       <c r="K7" s="84" t="str">
-        <f>SUBSTITUTE(F7, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-cs-chtintweb-lb-fe</v>
       </c>
       <c r="L7" s="84" t="s">
@@ -29367,7 +29391,7 @@
         <v>474</v>
       </c>
       <c r="Q7" s="85" t="str">
-        <f>SUBSTITUTE(F7, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-cs-chtintweb-lb-bp</v>
       </c>
     </row>
@@ -29402,7 +29426,7 @@
         <v>102</v>
       </c>
       <c r="K8" s="74" t="str">
-        <f>SUBSTITUTE(F8, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-cs-chtap-lb-fe</v>
       </c>
       <c r="L8" s="74" t="s">
@@ -29421,7 +29445,7 @@
         <v>472</v>
       </c>
       <c r="Q8" s="87" t="str">
-        <f>SUBSTITUTE(F8, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-cs-chtap-lb-bp</v>
       </c>
     </row>
@@ -29456,7 +29480,7 @@
         <v>102</v>
       </c>
       <c r="K9" s="84" t="str">
-        <f>SUBSTITUTE(F9, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-cs-chtweb-lb-fe</v>
       </c>
       <c r="L9" s="84" t="s">
@@ -29475,7 +29499,7 @@
         <v>473</v>
       </c>
       <c r="Q9" s="85" t="str">
-        <f>SUBSTITUTE(F9, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-cs-chtweb-lb-bp</v>
       </c>
     </row>
@@ -29510,7 +29534,7 @@
         <v>102</v>
       </c>
       <c r="K10" s="84" t="str">
-        <f>SUBSTITUTE(F10, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-drvmsgap-lb-fe</v>
       </c>
       <c r="L10" s="84" t="s">
@@ -29529,7 +29553,7 @@
         <v>449</v>
       </c>
       <c r="Q10" s="85" t="str">
-        <f>SUBSTITUTE(F10, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-drvmsgap-lb-bp</v>
       </c>
     </row>
@@ -29564,7 +29588,7 @@
         <v>102</v>
       </c>
       <c r="K11" s="74" t="str">
-        <f>SUBSTITUTE(F11, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-drvcltap-lb-fe</v>
       </c>
       <c r="L11" s="74" t="s">
@@ -29583,7 +29607,7 @@
         <v>447</v>
       </c>
       <c r="Q11" s="87" t="str">
-        <f>SUBSTITUTE(F11, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-drvcltap-lb-bp</v>
       </c>
     </row>
@@ -29618,7 +29642,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="84" t="str">
-        <f>SUBSTITUTE(F12, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-walkap-lb-fe</v>
       </c>
       <c r="L12" s="84" t="s">
@@ -29637,7 +29661,7 @@
         <v>446</v>
       </c>
       <c r="Q12" s="85" t="str">
-        <f>SUBSTITUTE(F12, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-walkap-lb-bp</v>
       </c>
     </row>
@@ -29672,7 +29696,7 @@
         <v>102</v>
       </c>
       <c r="K13" s="74" t="str">
-        <f>SUBSTITUTE(F13, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-bbimsgap-lb-fe</v>
       </c>
       <c r="L13" s="74" t="s">
@@ -29691,7 +29715,7 @@
         <v>445</v>
       </c>
       <c r="Q13" s="87" t="str">
-        <f>SUBSTITUTE(F13, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbimsgap-lb-bp</v>
       </c>
     </row>
@@ -29726,7 +29750,7 @@
         <v>102</v>
       </c>
       <c r="K14" s="84" t="str">
-        <f>SUBSTITUTE(F14, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-bbicltap-lb-fe</v>
       </c>
       <c r="L14" s="84" t="s">
@@ -29745,7 +29769,7 @@
         <v>444</v>
       </c>
       <c r="Q14" s="85" t="str">
-        <f>SUBSTITUTE(F14, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbicltap-lb-bp</v>
       </c>
     </row>
@@ -29780,7 +29804,7 @@
         <v>102</v>
       </c>
       <c r="K15" s="74" t="str">
-        <f>SUBSTITUTE(F15, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-adm-lb-fe</v>
       </c>
       <c r="L15" s="74" t="s">
@@ -29799,7 +29823,7 @@
         <v>443</v>
       </c>
       <c r="Q15" s="87" t="str">
-        <f>SUBSTITUTE(F15, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-adm-lb-bp</v>
       </c>
     </row>
@@ -29834,7 +29858,7 @@
         <v>102</v>
       </c>
       <c r="K16" s="84" t="str">
-        <f>SUBSTITUTE(F16, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-cmbsap-lb-fe</v>
       </c>
       <c r="L16" s="84" t="s">
@@ -29853,7 +29877,7 @@
         <v>454</v>
       </c>
       <c r="Q16" s="85" t="str">
-        <f>SUBSTITUTE(F16, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-cmbsap-lb-bp</v>
       </c>
     </row>
@@ -29888,7 +29912,7 @@
         <v>102</v>
       </c>
       <c r="K17" s="74" t="str">
-        <f>SUBSTITUTE(F17, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-cmsap-lb-fe</v>
       </c>
       <c r="L17" s="74" t="s">
@@ -29907,7 +29931,7 @@
         <v>452</v>
       </c>
       <c r="Q17" s="87" t="str">
-        <f>SUBSTITUTE(F17, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsap-lb-bp</v>
       </c>
     </row>
@@ -29942,7 +29966,7 @@
         <v>102</v>
       </c>
       <c r="K18" s="84" t="str">
-        <f>SUBSTITUTE(F18, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-cmsadm-lb-fe</v>
       </c>
       <c r="L18" s="84" t="s">
@@ -29961,7 +29985,7 @@
         <v>451</v>
       </c>
       <c r="Q18" s="85" t="str">
-        <f>SUBSTITUTE(F18, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsadm-lb-bp</v>
       </c>
     </row>
@@ -29996,7 +30020,7 @@
         <v>102</v>
       </c>
       <c r="K19" s="74" t="str">
-        <f>SUBSTITUTE(F19, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-ap-lb-fe</v>
       </c>
       <c r="L19" s="74" t="s">
@@ -30015,7 +30039,7 @@
         <v>442</v>
       </c>
       <c r="Q19" s="87" t="str">
-        <f>SUBSTITUTE(F19, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-ap-lb-bp</v>
       </c>
     </row>
@@ -30050,7 +30074,7 @@
         <v>102</v>
       </c>
       <c r="K20" s="84" t="str">
-        <f>SUBSTITUTE(F20, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-cmsweb-lb-fe</v>
       </c>
       <c r="L20" s="84" t="s">
@@ -30069,7 +30093,7 @@
         <v>453</v>
       </c>
       <c r="Q20" s="85" t="str">
-        <f>SUBSTITUTE(F20, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-cmsweb-lb-bp</v>
       </c>
     </row>
@@ -30104,7 +30128,7 @@
         <v>102</v>
       </c>
       <c r="K21" s="74" t="str">
-        <f>SUBSTITUTE(F21, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-web-lb-fe</v>
       </c>
       <c r="L21" s="74" t="s">
@@ -30123,7 +30147,7 @@
         <v>450</v>
       </c>
       <c r="Q21" s="87" t="str">
-        <f>SUBSTITUTE(F21, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-web-lb-bp</v>
       </c>
     </row>
@@ -30158,7 +30182,7 @@
         <v>102</v>
       </c>
       <c r="K22" s="84" t="str">
-        <f>SUBSTITUTE(F22, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-walkweb-lb-fe</v>
       </c>
       <c r="L22" s="84" t="s">
@@ -30177,7 +30201,7 @@
         <v>448</v>
       </c>
       <c r="Q22" s="85" t="str">
-        <f>SUBSTITUTE(F22, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-walkweb-lb-bp</v>
       </c>
     </row>
@@ -30212,7 +30236,7 @@
         <v>102</v>
       </c>
       <c r="K23" s="74" t="str">
-        <f>SUBSTITUTE(F23, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dis-bbiweb-lb-fe</v>
       </c>
       <c r="L23" s="74" t="s">
@@ -30231,7 +30255,7 @@
         <v>292</v>
       </c>
       <c r="Q23" s="87" t="str">
-        <f>SUBSTITUTE(F23, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dis-bbiweb-lb-bp</v>
       </c>
     </row>
@@ -30266,7 +30290,7 @@
         <v>102</v>
       </c>
       <c r="K24" s="74" t="str">
-        <f>SUBSTITUTE(F24, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-doip-adm-lb-fe</v>
       </c>
       <c r="L24" s="74" t="s">
@@ -30285,7 +30309,7 @@
         <v>477</v>
       </c>
       <c r="Q24" s="87" t="str">
-        <f>SUBSTITUTE(F24, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-doip-adm-lb-bp</v>
       </c>
     </row>
@@ -30320,7 +30344,7 @@
         <v>102</v>
       </c>
       <c r="K25" s="84" t="str">
-        <f>SUBSTITUTE(F25, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-doip-ap-lb-fe</v>
       </c>
       <c r="L25" s="84" t="s">
@@ -30339,7 +30363,7 @@
         <v>476</v>
       </c>
       <c r="Q25" s="85" t="str">
-        <f>SUBSTITUTE(F25, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-doip-ap-lb-bp</v>
       </c>
     </row>
@@ -30374,7 +30398,7 @@
         <v>102</v>
       </c>
       <c r="K26" s="74" t="str">
-        <f>SUBSTITUTE(F26, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-doip-web-lb-fe</v>
       </c>
       <c r="L26" s="74" t="s">
@@ -30393,7 +30417,7 @@
         <v>475</v>
       </c>
       <c r="Q26" s="87" t="str">
-        <f>SUBSTITUTE(F26, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-doip-web-lb-bp</v>
       </c>
     </row>
@@ -30428,7 +30452,7 @@
         <v>102</v>
       </c>
       <c r="K27" s="74" t="str">
-        <f>SUBSTITUTE(F27, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-admap-lb-fe</v>
       </c>
       <c r="L27" s="74" t="s">
@@ -30447,7 +30471,7 @@
         <v>461</v>
       </c>
       <c r="Q27" s="87" t="str">
-        <f>SUBSTITUTE(F27, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-admap-lb-bp</v>
       </c>
     </row>
@@ -30482,7 +30506,7 @@
         <v>102</v>
       </c>
       <c r="K28" s="84" t="str">
-        <f>SUBSTITUTE(F28, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-admweb-lb-fe</v>
       </c>
       <c r="L28" s="84" t="s">
@@ -30501,7 +30525,7 @@
         <v>460</v>
       </c>
       <c r="Q28" s="85" t="str">
-        <f>SUBSTITUTE(F28, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-admweb-lb-bp</v>
       </c>
     </row>
@@ -30536,7 +30560,7 @@
         <v>102</v>
       </c>
       <c r="K29" s="74" t="str">
-        <f>SUBSTITUTE(F29, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-geoap-lb-fe</v>
       </c>
       <c r="L29" s="74" t="s">
@@ -30555,7 +30579,7 @@
         <v>458</v>
       </c>
       <c r="Q29" s="87" t="str">
-        <f>SUBSTITUTE(F29, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-geoap-lb-bp</v>
       </c>
     </row>
@@ -30590,7 +30614,7 @@
         <v>102</v>
       </c>
       <c r="K30" s="84" t="str">
-        <f>SUBSTITUTE(F30, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-extgeoap-lb-fe</v>
       </c>
       <c r="L30" s="84" t="s">
@@ -30609,7 +30633,7 @@
         <v>457</v>
       </c>
       <c r="Q30" s="85" t="str">
-        <f>SUBSTITUTE(F30, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-extgeoap-lb-bp</v>
       </c>
     </row>
@@ -30644,7 +30668,7 @@
         <v>102</v>
       </c>
       <c r="K31" s="74" t="str">
-        <f>SUBSTITUTE(F31, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-ap-lb-fe</v>
       </c>
       <c r="L31" s="74" t="s">
@@ -30663,7 +30687,7 @@
         <v>456</v>
       </c>
       <c r="Q31" s="87" t="str">
-        <f>SUBSTITUTE(F31, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-ap-lb-bp</v>
       </c>
     </row>
@@ -30698,7 +30722,7 @@
         <v>102</v>
       </c>
       <c r="K32" s="84" t="str">
-        <f>SUBSTITUTE(F32, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-dprap-lb-fe</v>
       </c>
       <c r="L32" s="84" t="s">
@@ -30717,7 +30741,7 @@
         <v>469</v>
       </c>
       <c r="Q32" s="85" t="str">
-        <f>SUBSTITUTE(F32, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-dprap-lb-bp</v>
       </c>
     </row>
@@ -30752,7 +30776,7 @@
         <v>102</v>
       </c>
       <c r="K33" s="74" t="str">
-        <f>SUBSTITUTE(F33, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-diosweb-lb-fe</v>
       </c>
       <c r="L33" s="74" t="s">
@@ -30771,7 +30795,7 @@
         <v>467</v>
       </c>
       <c r="Q33" s="87" t="str">
-        <f>SUBSTITUTE(F33, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-diosweb-lb-bp</v>
       </c>
     </row>
@@ -30806,7 +30830,7 @@
         <v>102</v>
       </c>
       <c r="K34" s="84" t="str">
-        <f>SUBSTITUTE(F34, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-diosap-lb-fe</v>
       </c>
       <c r="L34" s="84" t="s">
@@ -30825,7 +30849,7 @@
         <v>466</v>
       </c>
       <c r="Q34" s="85" t="str">
-        <f>SUBSTITUTE(F34, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-diosap-lb-bp</v>
       </c>
     </row>
@@ -30860,7 +30884,7 @@
         <v>102</v>
       </c>
       <c r="K35" s="74" t="str">
-        <f>SUBSTITUTE(F35, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdsvadm-lb-fe</v>
       </c>
       <c r="L35" s="74" t="s">
@@ -30879,7 +30903,7 @@
         <v>465</v>
       </c>
       <c r="Q35" s="87" t="str">
-        <f>SUBSTITUTE(F35, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdsvadm-lb-bp</v>
       </c>
     </row>
@@ -30914,7 +30938,7 @@
         <v>102</v>
       </c>
       <c r="K36" s="84" t="str">
-        <f>SUBSTITUTE(F36, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdstap-lb-fe</v>
       </c>
       <c r="L36" s="84" t="s">
@@ -30933,7 +30957,7 @@
         <v>464</v>
       </c>
       <c r="Q36" s="85" t="str">
-        <f>SUBSTITUTE(F36, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdstap-lb-bp</v>
       </c>
     </row>
@@ -30968,7 +30992,7 @@
         <v>102</v>
       </c>
       <c r="K37" s="74" t="str">
-        <f>SUBSTITUTE(F37, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-cdmlap-lb-fe</v>
       </c>
       <c r="L37" s="74" t="s">
@@ -30987,7 +31011,7 @@
         <v>463</v>
       </c>
       <c r="Q37" s="87" t="str">
-        <f>SUBSTITUTE(F37, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-cdmlap-lb-bp</v>
       </c>
     </row>
@@ -31022,7 +31046,7 @@
         <v>102</v>
       </c>
       <c r="K38" s="84" t="str">
-        <f>SUBSTITUTE(F38, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-ingap-lb-fe</v>
       </c>
       <c r="L38" s="84" t="s">
@@ -31041,7 +31065,7 @@
         <v>455</v>
       </c>
       <c r="Q38" s="85" t="str">
-        <f>SUBSTITUTE(F38, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-ingap-lb-bp</v>
       </c>
     </row>
@@ -31076,7 +31100,7 @@
         <v>102</v>
       </c>
       <c r="K39" s="74" t="str">
-        <f>SUBSTITUTE(F39, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-dprweb-lb-fe</v>
       </c>
       <c r="L39" s="74" t="s">
@@ -31095,7 +31119,7 @@
         <v>468</v>
       </c>
       <c r="Q39" s="87" t="str">
-        <f>SUBSTITUTE(F39, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-dprweb-lb-bp</v>
       </c>
     </row>
@@ -31130,7 +31154,7 @@
         <v>102</v>
       </c>
       <c r="K40" s="84" t="str">
-        <f>SUBSTITUTE(F40, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-web-lb-fe</v>
       </c>
       <c r="L40" s="84" t="s">
@@ -31149,7 +31173,7 @@
         <v>462</v>
       </c>
       <c r="Q40" s="85" t="str">
-        <f>SUBSTITUTE(F40, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-web-lb-bp</v>
       </c>
     </row>
@@ -31184,7 +31208,7 @@
         <v>102</v>
       </c>
       <c r="K41" s="74" t="str">
-        <f>SUBSTITUTE(F41, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-dtg-mq-lb-fe</v>
       </c>
       <c r="L41" s="74" t="s">
@@ -31203,7 +31227,7 @@
         <v>459</v>
       </c>
       <c r="Q41" s="87" t="str">
-        <f>SUBSTITUTE(F41, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-dtg-mq-lb-bp</v>
       </c>
     </row>
@@ -31238,7 +31262,7 @@
         <v>102</v>
       </c>
       <c r="K42" s="84" t="str">
-        <f>SUBSTITUTE(F42, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-if-auth-lb-fe</v>
       </c>
       <c r="L42" s="84" t="s">
@@ -31257,7 +31281,7 @@
         <v>619</v>
       </c>
       <c r="Q42" s="85" t="str">
-        <f>SUBSTITUTE(F42, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-if-auth-lb-bp</v>
       </c>
     </row>
@@ -31292,7 +31316,7 @@
         <v>102</v>
       </c>
       <c r="K43" s="74" t="str">
-        <f>SUBSTITUTE(F43, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" si="0"/>
         <v>t-if-proxy-lb-fe</v>
       </c>
       <c r="L43" s="74" t="s">
@@ -31311,27 +31335,61 @@
         <v>623</v>
       </c>
       <c r="Q43" s="87" t="str">
-        <f>SUBSTITUTE(F43, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-if-proxy-lb-bp</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="B44" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="93" t="s">
+        <v>634</v>
+      </c>
+      <c r="D44" s="93" t="s">
+        <v>629</v>
+      </c>
+      <c r="E44" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="93" t="s">
+        <v>630</v>
+      </c>
+      <c r="G44" s="93" t="s">
+        <v>111</v>
+      </c>
+      <c r="H44" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="I44" s="93" t="s">
+        <v>631</v>
+      </c>
+      <c r="J44" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="K44" s="93" t="str">
+        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe2"</f>
+        <v>t-com-auth-lb-fe2</v>
+      </c>
+      <c r="L44" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="M44" s="93" t="s">
+        <v>201</v>
+      </c>
+      <c r="N44" s="93" t="s">
+        <v>632</v>
+      </c>
+      <c r="O44" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="P44" s="93" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q44" s="93" t="str">
+        <f t="shared" si="1"/>
+        <v>t-com-auth-lb-bp</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
@@ -34239,21 +34297,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34397,10 +34440,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34422,19 +34490,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C68D1B-E5D6-45FB-A91A-A4A92D0FC548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3218CA96-007F-4871-9311-3EFF2C5850C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3975,11 +3975,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.157.165.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.162.15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -29102,7 +29102,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="74" t="str">
-        <f t="shared" ref="K2:K44" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="K2:K43" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="L2" s="74" t="s">
@@ -31344,7 +31344,7 @@
         <v>183</v>
       </c>
       <c r="C44" s="93" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D44" s="93" t="s">
         <v>629</v>
@@ -31384,7 +31384,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="93" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Q44" s="93" t="str">
         <f t="shared" si="1"/>
@@ -34297,6 +34297,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34440,35 +34455,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34490,9 +34480,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3218CA96-007F-4871-9311-3EFF2C5850C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9909308B-F757-4A3E-B005-F458D0FDD99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4821" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4821" uniqueCount="634">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3963,23 +3963,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-t-com-auth-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>t-com-ap-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.157.162.15</t>
+    <t>hazr-t-com-proxy-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.134.15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31344,7 +31340,7 @@
         <v>183</v>
       </c>
       <c r="C44" s="93" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D44" s="93" t="s">
         <v>629</v>
@@ -31353,7 +31349,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="93" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G44" s="93" t="s">
         <v>111</v>
@@ -31362,33 +31358,33 @@
         <v>125</v>
       </c>
       <c r="I44" s="93" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="J44" s="93" t="s">
         <v>102</v>
       </c>
       <c r="K44" s="93" t="str">
         <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe2"</f>
-        <v>t-com-auth-lb-fe2</v>
+        <v>t-com-proxy-lb-fe2</v>
       </c>
       <c r="L44" s="93" t="s">
         <v>199</v>
       </c>
       <c r="M44" s="93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N44" s="93" t="s">
-        <v>632</v>
+        <v>337</v>
       </c>
       <c r="O44" s="93" t="s">
         <v>108</v>
       </c>
       <c r="P44" s="93" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="Q44" s="93" t="str">
         <f t="shared" si="1"/>
-        <v>t-com-auth-lb-bp</v>
+        <v>t-com-proxy-lb-bp</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -34297,21 +34293,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34455,10 +34436,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34480,19 +34486,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9909308B-F757-4A3E-B005-F458D0FDD99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4002F83-E9ED-4AA0-B832-D6B35C5068DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4821" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="635">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3976,6 +3976,10 @@
   </si>
   <si>
     <t>10.157.134.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.134.10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -31364,8 +31368,8 @@
         <v>102</v>
       </c>
       <c r="K44" s="93" t="str">
-        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe2"</f>
-        <v>t-com-proxy-lb-fe2</v>
+        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe"</f>
+        <v>t-com-proxy-lb-fe</v>
       </c>
       <c r="L44" s="93" t="s">
         <v>199</v>
@@ -31380,7 +31384,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="93" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Q44" s="93" t="str">
         <f t="shared" si="1"/>
@@ -31388,22 +31392,56 @@
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
+      <c r="B45" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="D45" s="93" t="s">
+        <v>629</v>
+      </c>
+      <c r="E45" s="93" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="93" t="s">
+        <v>632</v>
+      </c>
+      <c r="G45" s="93" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="I45" s="93" t="s">
+        <v>628</v>
+      </c>
+      <c r="J45" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="K45" s="93" t="str">
+        <f>SUBSTITUTE(F45, "hazr-", "")&amp;"-fe2"</f>
+        <v>t-com-proxy-lb-fe2</v>
+      </c>
+      <c r="L45" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="M45" s="93" t="s">
+        <v>200</v>
+      </c>
+      <c r="N45" s="93" t="s">
+        <v>337</v>
+      </c>
+      <c r="O45" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="P45" s="93" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q45" s="93" t="str">
+        <f t="shared" ref="Q45" si="2">SUBSTITUTE(F45, "hazr-", "")&amp;"-bp"</f>
+        <v>t-com-proxy-lb-bp</v>
+      </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
@@ -34293,6 +34331,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34436,35 +34489,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34486,9 +34514,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62B147F-4278-41CA-AB07-AE98DA422A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB738B8-8E90-4199-AE65-DD722E00C1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="635">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4474,7 +4474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4810,6 +4810,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29121,7 +29124,7 @@
         <v>479</v>
       </c>
       <c r="Q2" s="87" t="str">
-        <f t="shared" ref="Q2:Q44" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="Q2:Q45" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
     </row>
@@ -31340,18 +31343,11 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="C44" s="93" t="s">
-        <v>630</v>
-      </c>
-      <c r="D44" s="93" t="s">
-        <v>628</v>
-      </c>
-      <c r="E44" s="93" t="s">
-        <v>24</v>
-      </c>
+      <c r="A44" s="97"/>
+      <c r="B44" s="112"/>
+      <c r="C44" s="112"/>
+      <c r="D44" s="112"/>
+      <c r="E44" s="112"/>
       <c r="F44" s="93" t="s">
         <v>631</v>
       </c>
@@ -31362,14 +31358,14 @@
         <v>634</v>
       </c>
       <c r="I44" s="93" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J44" s="93" t="s">
         <v>102</v>
       </c>
       <c r="K44" s="93" t="str">
-        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe"</f>
-        <v>t-com-proxy-lb-fe</v>
+        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe2"</f>
+        <v>t-com-proxy-lb-fe2</v>
       </c>
       <c r="L44" s="93" t="s">
         <v>198</v>
@@ -31384,7 +31380,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="93" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q44" s="93" t="str">
         <f t="shared" si="1"/>
@@ -31396,7 +31392,7 @@
         <v>182</v>
       </c>
       <c r="C45" s="93" t="s">
-        <v>182</v>
+        <v>630</v>
       </c>
       <c r="D45" s="93" t="s">
         <v>628</v>
@@ -31414,14 +31410,14 @@
         <v>634</v>
       </c>
       <c r="I45" s="93" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J45" s="93" t="s">
         <v>102</v>
       </c>
       <c r="K45" s="93" t="str">
-        <f>SUBSTITUTE(F45, "hazr-", "")&amp;"-fe2"</f>
-        <v>t-com-proxy-lb-fe2</v>
+        <f>SUBSTITUTE(F45, "hazr-", "")&amp;"-fe"</f>
+        <v>t-com-proxy-lb-fe</v>
       </c>
       <c r="L45" s="93" t="s">
         <v>198</v>
@@ -31436,10 +31432,10 @@
         <v>108</v>
       </c>
       <c r="P45" s="93" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q45" s="93" t="str">
-        <f t="shared" ref="Q45" si="2">SUBSTITUTE(F45, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" si="1"/>
         <v>t-com-proxy-lb-bp</v>
       </c>
     </row>
@@ -31487,6 +31483,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34331,6 +34328,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34474,35 +34486,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34524,9 +34511,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB738B8-8E90-4199-AE65-DD722E00C1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3DDC52-A43F-45B0-9514-A7EA829BE9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4833" uniqueCount="641">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3955,7 +3955,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-t-com-rg</t>
+    <t>ZoneRedundant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PULS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3963,23 +3971,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TEST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-com-proxy-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.134.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.134.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZoneRedundant</t>
+    <t>t-puls-ap-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.147.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PULS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-puls-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PULS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-puls-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-puls-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tcp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4119,7 +4143,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4183,6 +4207,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4474,7 +4504,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4811,7 +4841,13 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6833,7 +6869,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:R87"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
@@ -10702,7 +10738,7 @@
         <v>t-dip-ap-lb-rule8200</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F87" si="14">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="F65:F88" si="14">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -10715,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="74" t="str">
-        <f t="shared" ref="J65:J87" si="15">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="J65:J88" si="15">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K65" s="74">
@@ -11464,7 +11500,7 @@
         <v>443</v>
       </c>
       <c r="L78" s="84" t="str">
-        <f t="shared" ref="L78:L87" si="17">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
+        <f t="shared" ref="L78:L88" si="17">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
         <v>t-if-proxy-lb-pb443</v>
       </c>
       <c r="M78" s="84" t="s">
@@ -12032,6 +12068,66 @@
         <v>1</v>
       </c>
       <c r="R87" s="84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A88" s="113" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C88" s="113" t="s">
+        <v>637</v>
+      </c>
+      <c r="D88" s="113" t="s">
+        <v>638</v>
+      </c>
+      <c r="E88" s="1" t="str">
+        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-rule"&amp;N88</f>
+        <v>t-puls-lb-rule442</v>
+      </c>
+      <c r="F88" s="113" t="str">
+        <f t="shared" si="14"/>
+        <v>t-puls-lb-fe</v>
+      </c>
+      <c r="G88" s="113" t="s">
+        <v>639</v>
+      </c>
+      <c r="H88" s="113">
+        <v>442</v>
+      </c>
+      <c r="I88" s="114" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" s="113" t="str">
+        <f t="shared" si="15"/>
+        <v>t-puls-lb-bp</v>
+      </c>
+      <c r="K88" s="113">
+        <v>442</v>
+      </c>
+      <c r="L88" s="113" t="str">
+        <f t="shared" si="17"/>
+        <v>t-puls-lb-pb442</v>
+      </c>
+      <c r="M88" s="113" t="s">
+        <v>640</v>
+      </c>
+      <c r="N88" s="113">
+        <v>442</v>
+      </c>
+      <c r="O88" s="113">
+        <v>4</v>
+      </c>
+      <c r="P88" s="113" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q88" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R88" s="113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29003,7 +29099,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.25" customWidth="1"/>
@@ -29096,7 +29192,7 @@
         <v>111</v>
       </c>
       <c r="H2" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I2" s="74" t="s">
         <v>627</v>
@@ -29105,7 +29201,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="74" t="str">
-        <f t="shared" ref="K2:K43" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="K2:K44" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="L2" s="74" t="s">
@@ -29124,7 +29220,7 @@
         <v>479</v>
       </c>
       <c r="Q2" s="87" t="str">
-        <f t="shared" ref="Q2:Q45" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="Q2:Q44" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
     </row>
@@ -29150,7 +29246,7 @@
         <v>111</v>
       </c>
       <c r="H3" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I3" s="84" t="s">
         <v>627</v>
@@ -29204,7 +29300,7 @@
         <v>111</v>
       </c>
       <c r="H4" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I4" s="74" t="s">
         <v>627</v>
@@ -29258,7 +29354,7 @@
         <v>111</v>
       </c>
       <c r="H5" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>627</v>
@@ -29312,7 +29408,7 @@
         <v>111</v>
       </c>
       <c r="H6" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I6" s="84" t="s">
         <v>627</v>
@@ -29366,7 +29462,7 @@
         <v>111</v>
       </c>
       <c r="H7" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I7" s="84" t="s">
         <v>627</v>
@@ -29420,7 +29516,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>627</v>
@@ -29474,7 +29570,7 @@
         <v>111</v>
       </c>
       <c r="H9" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I9" s="84" t="s">
         <v>627</v>
@@ -29528,7 +29624,7 @@
         <v>111</v>
       </c>
       <c r="H10" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I10" s="84" t="s">
         <v>627</v>
@@ -29582,7 +29678,7 @@
         <v>111</v>
       </c>
       <c r="H11" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I11" s="74" t="s">
         <v>627</v>
@@ -29636,7 +29732,7 @@
         <v>111</v>
       </c>
       <c r="H12" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I12" s="84" t="s">
         <v>627</v>
@@ -29690,7 +29786,7 @@
         <v>111</v>
       </c>
       <c r="H13" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I13" s="74" t="s">
         <v>627</v>
@@ -29744,7 +29840,7 @@
         <v>111</v>
       </c>
       <c r="H14" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I14" s="84" t="s">
         <v>627</v>
@@ -29798,7 +29894,7 @@
         <v>111</v>
       </c>
       <c r="H15" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I15" s="74" t="s">
         <v>627</v>
@@ -29852,7 +29948,7 @@
         <v>111</v>
       </c>
       <c r="H16" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I16" s="84" t="s">
         <v>627</v>
@@ -29906,7 +30002,7 @@
         <v>111</v>
       </c>
       <c r="H17" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I17" s="74" t="s">
         <v>627</v>
@@ -29960,7 +30056,7 @@
         <v>111</v>
       </c>
       <c r="H18" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I18" s="84" t="s">
         <v>627</v>
@@ -30014,7 +30110,7 @@
         <v>111</v>
       </c>
       <c r="H19" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I19" s="74" t="s">
         <v>627</v>
@@ -30068,7 +30164,7 @@
         <v>111</v>
       </c>
       <c r="H20" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I20" s="84" t="s">
         <v>627</v>
@@ -30122,7 +30218,7 @@
         <v>111</v>
       </c>
       <c r="H21" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I21" s="74" t="s">
         <v>627</v>
@@ -30176,7 +30272,7 @@
         <v>111</v>
       </c>
       <c r="H22" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I22" s="84" t="s">
         <v>627</v>
@@ -30230,7 +30326,7 @@
         <v>111</v>
       </c>
       <c r="H23" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I23" s="74" t="s">
         <v>627</v>
@@ -30284,7 +30380,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I24" s="74" t="s">
         <v>627</v>
@@ -30338,7 +30434,7 @@
         <v>111</v>
       </c>
       <c r="H25" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I25" s="84" t="s">
         <v>627</v>
@@ -30392,7 +30488,7 @@
         <v>111</v>
       </c>
       <c r="H26" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I26" s="74" t="s">
         <v>627</v>
@@ -30446,7 +30542,7 @@
         <v>111</v>
       </c>
       <c r="H27" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I27" s="74" t="s">
         <v>627</v>
@@ -30500,7 +30596,7 @@
         <v>111</v>
       </c>
       <c r="H28" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I28" s="84" t="s">
         <v>627</v>
@@ -30554,7 +30650,7 @@
         <v>111</v>
       </c>
       <c r="H29" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I29" s="74" t="s">
         <v>627</v>
@@ -30608,7 +30704,7 @@
         <v>111</v>
       </c>
       <c r="H30" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I30" s="84" t="s">
         <v>627</v>
@@ -30662,7 +30758,7 @@
         <v>111</v>
       </c>
       <c r="H31" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I31" s="74" t="s">
         <v>627</v>
@@ -30716,7 +30812,7 @@
         <v>111</v>
       </c>
       <c r="H32" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I32" s="84" t="s">
         <v>627</v>
@@ -30770,7 +30866,7 @@
         <v>111</v>
       </c>
       <c r="H33" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I33" s="74" t="s">
         <v>627</v>
@@ -30824,7 +30920,7 @@
         <v>111</v>
       </c>
       <c r="H34" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I34" s="84" t="s">
         <v>627</v>
@@ -30878,7 +30974,7 @@
         <v>111</v>
       </c>
       <c r="H35" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I35" s="74" t="s">
         <v>627</v>
@@ -30932,7 +31028,7 @@
         <v>111</v>
       </c>
       <c r="H36" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I36" s="84" t="s">
         <v>627</v>
@@ -30986,7 +31082,7 @@
         <v>111</v>
       </c>
       <c r="H37" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I37" s="74" t="s">
         <v>627</v>
@@ -31040,7 +31136,7 @@
         <v>111</v>
       </c>
       <c r="H38" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I38" s="84" t="s">
         <v>627</v>
@@ -31094,7 +31190,7 @@
         <v>111</v>
       </c>
       <c r="H39" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I39" s="74" t="s">
         <v>627</v>
@@ -31148,7 +31244,7 @@
         <v>111</v>
       </c>
       <c r="H40" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I40" s="84" t="s">
         <v>627</v>
@@ -31202,7 +31298,7 @@
         <v>111</v>
       </c>
       <c r="H41" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I41" s="74" t="s">
         <v>627</v>
@@ -31256,7 +31352,7 @@
         <v>111</v>
       </c>
       <c r="H42" s="84" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I42" s="84" t="s">
         <v>627</v>
@@ -31310,7 +31406,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I43" s="74" t="s">
         <v>627</v>
@@ -31343,137 +31439,75 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="97"/>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
+      <c r="A44" s="112"/>
+      <c r="B44" s="93" t="s">
+        <v>629</v>
+      </c>
+      <c r="C44" s="93" t="s">
+        <v>630</v>
+      </c>
+      <c r="D44" s="93" t="s">
+        <v>481</v>
+      </c>
+      <c r="E44" s="93" t="s">
+        <v>24</v>
+      </c>
       <c r="F44" s="93" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="G44" s="93" t="s">
         <v>111</v>
       </c>
       <c r="H44" s="93" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I44" s="93" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="J44" s="93" t="s">
         <v>102</v>
       </c>
       <c r="K44" s="93" t="str">
-        <f>SUBSTITUTE(F44, "hazr-", "")&amp;"-fe2"</f>
-        <v>t-com-proxy-lb-fe2</v>
+        <f t="shared" si="0"/>
+        <v>t-puls-lb-fe</v>
       </c>
       <c r="L44" s="93" t="s">
         <v>198</v>
       </c>
       <c r="M44" s="93" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N44" s="93" t="s">
-        <v>336</v>
+        <v>632</v>
       </c>
       <c r="O44" s="93" t="s">
         <v>108</v>
       </c>
       <c r="P44" s="93" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Q44" s="93" t="str">
         <f t="shared" si="1"/>
-        <v>t-com-proxy-lb-bp</v>
+        <v>t-puls-lb-bp</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="C45" s="93" t="s">
-        <v>630</v>
-      </c>
-      <c r="D45" s="93" t="s">
-        <v>628</v>
-      </c>
-      <c r="E45" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="93" t="s">
-        <v>631</v>
-      </c>
-      <c r="G45" s="93" t="s">
-        <v>111</v>
-      </c>
-      <c r="H45" s="93" t="s">
-        <v>634</v>
-      </c>
-      <c r="I45" s="93" t="s">
-        <v>629</v>
-      </c>
-      <c r="J45" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="K45" s="93" t="str">
-        <f>SUBSTITUTE(F45, "hazr-", "")&amp;"-fe"</f>
-        <v>t-com-proxy-lb-fe</v>
-      </c>
-      <c r="L45" s="93" t="s">
-        <v>198</v>
-      </c>
-      <c r="M45" s="93" t="s">
-        <v>199</v>
-      </c>
-      <c r="N45" s="93" t="s">
-        <v>336</v>
-      </c>
-      <c r="O45" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="P45" s="93" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q45" s="93" t="str">
-        <f t="shared" si="1"/>
-        <v>t-com-proxy-lb-bp</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:Q43" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
@@ -31489,7 +31523,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E6DC6D-4CAC-4686-B15B-DE2A4B4502D8}">
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
@@ -33605,7 +33639,7 @@
         <v>371</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F87" si="3">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
+        <f t="shared" ref="F65:F88" si="3">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -34318,6 +34352,38 @@
         <v>5</v>
       </c>
       <c r="K87" s="84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="112"/>
+      <c r="B88" s="114" t="s">
+        <v>182</v>
+      </c>
+      <c r="C88" s="48" t="s">
+        <v>634</v>
+      </c>
+      <c r="D88" s="114" t="s">
+        <v>481</v>
+      </c>
+      <c r="E88" s="114" t="s">
+        <v>635</v>
+      </c>
+      <c r="F88" s="114" t="str">
+        <f t="shared" si="3"/>
+        <v>t-puls-lb-pb442</v>
+      </c>
+      <c r="G88" s="114" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88" s="114">
+        <v>442</v>
+      </c>
+      <c r="I88" s="48"/>
+      <c r="J88" s="114">
+        <v>5</v>
+      </c>
+      <c r="K88" s="114">
         <v>2</v>
       </c>
     </row>
@@ -34328,21 +34394,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34486,10 +34537,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34511,19 +34587,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3DDC52-A43F-45B0-9514-A7EA829BE9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903F33D-CAF4-4626-AED0-B7E534213CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -4504,7 +4504,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4844,10 +4844,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12098,7 +12095,7 @@
       <c r="H88" s="113">
         <v>442</v>
       </c>
-      <c r="I88" s="114" t="b">
+      <c r="I88" s="74" t="b">
         <v>0</v>
       </c>
       <c r="J88" s="113" t="str">
@@ -34357,33 +34354,33 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="112"/>
-      <c r="B88" s="114" t="s">
+      <c r="B88" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C88" s="48" t="s">
         <v>634</v>
       </c>
-      <c r="D88" s="114" t="s">
+      <c r="D88" s="74" t="s">
         <v>481</v>
       </c>
-      <c r="E88" s="114" t="s">
+      <c r="E88" s="74" t="s">
         <v>635</v>
       </c>
-      <c r="F88" s="114" t="str">
+      <c r="F88" s="74" t="str">
         <f t="shared" si="3"/>
         <v>t-puls-lb-pb442</v>
       </c>
-      <c r="G88" s="114" t="s">
+      <c r="G88" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="H88" s="114">
+      <c r="H88" s="74">
         <v>442</v>
       </c>
       <c r="I88" s="48"/>
-      <c r="J88" s="114">
+      <c r="J88" s="74">
         <v>5</v>
       </c>
-      <c r="K88" s="114">
+      <c r="K88" s="74">
         <v>2</v>
       </c>
     </row>
@@ -34394,6 +34391,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34537,35 +34549,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34587,9 +34574,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903F33D-CAF4-4626-AED0-B7E534213CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD5371-156E-4160-A7B5-BAF374BB6770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4833" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="629">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3956,54 +3956,6 @@
   </si>
   <si>
     <t>ZoneRedundant</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PULS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-puls-ap-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.147.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PULS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-puls-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PULS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-puls-rg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-puls-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tcp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4143,7 +4095,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4201,18 +4153,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4504,7 +4444,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4837,15 +4777,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6866,7 +6797,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
@@ -10735,7 +10666,7 @@
         <v>t-dip-ap-lb-rule8200</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F88" si="14">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="F65:F87" si="14">SUBSTITUTE(D65, "hazr-", "")&amp;"-fe"</f>
         <v>t-dip-ap-lb-fe</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -10748,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="74" t="str">
-        <f t="shared" ref="J65:J88" si="15">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="J65:J87" si="15">SUBSTITUTE(D65, "hazr-", "")&amp;"-bp"</f>
         <v>t-dip-ap-lb-bp</v>
       </c>
       <c r="K65" s="74">
@@ -11497,7 +11428,7 @@
         <v>443</v>
       </c>
       <c r="L78" s="84" t="str">
-        <f t="shared" ref="L78:L88" si="17">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
+        <f t="shared" ref="L78:L87" si="17">SUBSTITUTE(D78, "hazr-", "")&amp;"-pb"&amp;IF(N78="", "", N78)</f>
         <v>t-if-proxy-lb-pb443</v>
       </c>
       <c r="M78" s="84" t="s">
@@ -12065,66 +11996,6 @@
         <v>1</v>
       </c>
       <c r="R87" s="84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A88" s="113" t="s">
-        <v>182</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C88" s="113" t="s">
-        <v>637</v>
-      </c>
-      <c r="D88" s="113" t="s">
-        <v>638</v>
-      </c>
-      <c r="E88" s="1" t="str">
-        <f>SUBSTITUTE(D88, "hazr-", "")&amp;"-rule"&amp;N88</f>
-        <v>t-puls-lb-rule442</v>
-      </c>
-      <c r="F88" s="113" t="str">
-        <f t="shared" si="14"/>
-        <v>t-puls-lb-fe</v>
-      </c>
-      <c r="G88" s="113" t="s">
-        <v>639</v>
-      </c>
-      <c r="H88" s="113">
-        <v>442</v>
-      </c>
-      <c r="I88" s="74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" s="113" t="str">
-        <f t="shared" si="15"/>
-        <v>t-puls-lb-bp</v>
-      </c>
-      <c r="K88" s="113">
-        <v>442</v>
-      </c>
-      <c r="L88" s="113" t="str">
-        <f t="shared" si="17"/>
-        <v>t-puls-lb-pb442</v>
-      </c>
-      <c r="M88" s="113" t="s">
-        <v>640</v>
-      </c>
-      <c r="N88" s="113">
-        <v>442</v>
-      </c>
-      <c r="O88" s="113">
-        <v>4</v>
-      </c>
-      <c r="P88" s="113" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q88" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R88" s="113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29096,7 +28967,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.25" customWidth="1"/>
@@ -29198,7 +29069,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="74" t="str">
-        <f t="shared" ref="K2:K44" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
+        <f t="shared" ref="K2:K43" si="0">SUBSTITUTE(F2, "hazr-", "")&amp;"-fe"</f>
         <v>t-bdp-crkml-lb-fe</v>
       </c>
       <c r="L2" s="74" t="s">
@@ -29217,7 +29088,7 @@
         <v>479</v>
       </c>
       <c r="Q2" s="87" t="str">
-        <f t="shared" ref="Q2:Q44" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
+        <f t="shared" ref="Q2:Q43" si="1">SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
         <v>t-bdp-crkml-lb-bp</v>
       </c>
     </row>
@@ -29276,7 +29147,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="111"/>
+      <c r="A4" s="97"/>
       <c r="B4" s="74" t="s">
         <v>182</v>
       </c>
@@ -29385,54 +29256,54 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="97"/>
-      <c r="B6" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" s="84" t="str" cm="1">
+      <c r="B6" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="74" t="str" cm="1">
         <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="74" t="s">
         <v>386</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="84" t="s">
+      <c r="F6" s="74" t="s">
         <v>382</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="84" t="s">
+      <c r="H6" s="74" t="s">
         <v>628</v>
       </c>
-      <c r="I6" s="84" t="s">
+      <c r="I6" s="74" t="s">
         <v>627</v>
       </c>
-      <c r="J6" s="84" t="s">
+      <c r="J6" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K6" s="84" t="str">
+      <c r="K6" s="74" t="str">
         <f t="shared" si="0"/>
         <v>t-bdp-crkweb-lb-fe</v>
       </c>
-      <c r="L6" s="84" t="s">
-        <v>198</v>
-      </c>
-      <c r="M6" s="84" t="s">
+      <c r="L6" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="M6" s="74" t="s">
         <v>199</v>
       </c>
-      <c r="N6" s="84" t="s">
+      <c r="N6" s="74" t="s">
         <v>332</v>
       </c>
-      <c r="O6" s="84" t="s">
+      <c r="O6" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P6" s="84" t="s">
+      <c r="P6" s="74" t="s">
         <v>477</v>
       </c>
-      <c r="Q6" s="85" t="str">
+      <c r="Q6" s="87" t="str">
         <f t="shared" si="1"/>
         <v>t-bdp-crkweb-lb-bp</v>
       </c>
@@ -30950,7 +30821,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="111"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="74" t="s">
         <v>182</v>
       </c>
@@ -31436,75 +31307,22 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="112"/>
-      <c r="B44" s="93" t="s">
-        <v>629</v>
-      </c>
-      <c r="C44" s="93" t="s">
-        <v>630</v>
-      </c>
-      <c r="D44" s="93" t="s">
-        <v>481</v>
-      </c>
-      <c r="E44" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="93" t="s">
-        <v>635</v>
-      </c>
-      <c r="G44" s="93" t="s">
-        <v>111</v>
-      </c>
-      <c r="H44" s="93" t="s">
-        <v>628</v>
-      </c>
-      <c r="I44" s="93" t="s">
-        <v>631</v>
-      </c>
-      <c r="J44" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="K44" s="93" t="str">
-        <f t="shared" si="0"/>
-        <v>t-puls-lb-fe</v>
-      </c>
-      <c r="L44" s="93" t="s">
-        <v>198</v>
-      </c>
-      <c r="M44" s="93" t="s">
-        <v>200</v>
-      </c>
-      <c r="N44" s="93" t="s">
-        <v>632</v>
-      </c>
-      <c r="O44" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="P44" s="93" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q44" s="93" t="str">
-        <f t="shared" si="1"/>
-        <v>t-puls-lb-bp</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:Q43" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
@@ -31520,7 +31338,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E6DC6D-4CAC-4686-B15B-DE2A4B4502D8}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
@@ -32228,10 +32046,7 @@
       <c r="B22" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="84" t="str" cm="1">
-        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
-        <v>DTG</v>
-      </c>
+      <c r="C22" s="84"/>
       <c r="D22" s="84" t="s">
         <v>385</v>
       </c>
@@ -32421,10 +32236,7 @@
       <c r="B28" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="84" t="str" cm="1">
-        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
-        <v>DOIP</v>
-      </c>
+      <c r="C28" s="84"/>
       <c r="D28" s="84" t="s">
         <v>388</v>
       </c>
@@ -32449,10 +32261,7 @@
       <c r="B29" s="86" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="86" t="str" cm="1">
-        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
-        <v>DOIP</v>
-      </c>
+      <c r="C29" s="86"/>
       <c r="D29" s="86" t="s">
         <v>388</v>
       </c>
@@ -32477,10 +32286,7 @@
       <c r="B30" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="84" t="str" cm="1">
-        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
-        <v>DOIP</v>
-      </c>
+      <c r="C30" s="84"/>
       <c r="D30" s="84" t="s">
         <v>388</v>
       </c>
@@ -33636,7 +33442,7 @@
         <v>371</v>
       </c>
       <c r="F65" s="74" t="str">
-        <f t="shared" ref="F65:F88" si="3">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
+        <f t="shared" ref="F65:F87" si="3">SUBSTITUTE(E65, "hazr-", "")&amp;"-pb"&amp;H65</f>
         <v>t-dip-ap-lb-pb8200</v>
       </c>
       <c r="G65" s="74" t="s">
@@ -34349,38 +34155,6 @@
         <v>5</v>
       </c>
       <c r="K87" s="84">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="112"/>
-      <c r="B88" s="74" t="s">
-        <v>182</v>
-      </c>
-      <c r="C88" s="48" t="s">
-        <v>634</v>
-      </c>
-      <c r="D88" s="74" t="s">
-        <v>481</v>
-      </c>
-      <c r="E88" s="74" t="s">
-        <v>635</v>
-      </c>
-      <c r="F88" s="74" t="str">
-        <f t="shared" si="3"/>
-        <v>t-puls-lb-pb442</v>
-      </c>
-      <c r="G88" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="H88" s="74">
-        <v>442</v>
-      </c>
-      <c r="I88" s="48"/>
-      <c r="J88" s="74">
-        <v>5</v>
-      </c>
-      <c r="K88" s="74">
         <v>2</v>
       </c>
     </row>

--- a/서버정보/20260521_리소스배포_테스트.xlsx
+++ b/서버정보/20260521_리소스배포_테스트.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD5371-156E-4160-A7B5-BAF374BB6770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -34165,21 +34165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -34323,10 +34308,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34348,19 +34358,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>